--- a/Excel/Diy优胜/恶堕凛视.xlsx
+++ b/Excel/Diy优胜/恶堕凛视.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA976A2C-E789-4313-B5EA-B48277C5E010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F10D07-957A-4A6B-9FEE-202BEE93DC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="OLE_LINK2" localSheetId="2">SkillData!$E$17</definedName>
+    <definedName name="OLE_LINK2" localSheetId="2">SkillData!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="505">
   <si>
     <t>Id</t>
   </si>
@@ -1729,10 +1729,6 @@
     <t>凛视未部署</t>
   </si>
   <si>
-    <t>凛视未部署</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>0,0</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -1745,19 +1741,7 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>标记未部署地块</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>冒黑雾</t>
-  </si>
-  <si>
-    <t>自身距离降序</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取非线性移动,标记未部署地块</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>string[]</t>
@@ -1784,23 +1768,128 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>叠层转换</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>空buff</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>{"MaxLevel":3,"BuffId":空buff}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>标记当前部署地块</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>标记已部署地块</t>
+    <t>放置升序</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>-凛视降临</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>标记已部署地块,标记当前部署地块,闪现</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>标记已部署地块,标记当前部署地块</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>叠层转化</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MaxLevel":2,"BuffId":"空buff"}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用地板</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>全地形</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔓延性坍缩</t>
+  </si>
+  <si>
+    <t>蔓延性坍缩</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Color":"#302F4B","Alpha":0.5}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>远见</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>悲哀的眼窥视厄运，扭曲的未来正吞噬辉光</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>凛视获取攻击范围</t>
+  </si>
+  <si>
+    <t>凛视获取攻击范围</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取额外攻击范围</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>凛视普攻</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>终点距离</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟随攻击</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>史都华德弹道</t>
+  </si>
+  <si>
+    <t>Muzzle</t>
+  </si>
+  <si>
+    <t>获取蔓延性坍缩</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"UnitId":"蔓延性坍缩","Count":12,"MaxCount":12}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>凛视普攻,凛视获取攻击范围,获取蔓延性坍缩,获取非线性移动,标记当前部署地块,标记已部署地块,闪现</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"技能Id列表":["凛视普攻"]}</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>凛视重置攻击范围</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>即死</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1968,7 +2057,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2022,6 +2111,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2490,7 +2582,7 @@
         <v>27</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="AN1" t="s">
         <v>28</v>
@@ -2654,7 +2746,7 @@
         <v>79</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="AN2" t="s">
         <v>80</v>
@@ -2860,7 +2952,7 @@
         <v>112</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="AN3" t="s">
         <v>113</v>
@@ -3010,7 +3102,7 @@
         <v>122</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AJ5" s="2" t="s">
         <v>437</v>
@@ -3019,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -3137,7 +3229,7 @@
         <v>3</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AN6">
         <v>0</v>
@@ -3188,18 +3280,111 @@
       </c>
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>445</v>
+      </c>
       <c r="E7" s="12"/>
-      <c r="F7" s="2"/>
-      <c r="AG7" s="17"/>
-      <c r="AH7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>90</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0.05</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>443</v>
+      </c>
       <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
+      <c r="AJ7" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="AK7">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0.5</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
       <c r="AU7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BC7" s="2"/>
-      <c r="BK7" s="2"/>
+      <c r="AV7">
+        <v>0.25</v>
+      </c>
+      <c r="BA7" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="BC7" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="BD7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG7">
+        <v>6</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>485</v>
+      </c>
       <c r="BL7" s="2"/>
       <c r="BM7" s="2"/>
       <c r="BO7" s="2"/>
@@ -6050,7 +6235,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ831"/>
+  <dimension ref="A1:DJ835"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -7183,8 +7368,11 @@
       <c r="X6" s="5">
         <v>1</v>
       </c>
+      <c r="BO6" s="2" t="s">
+        <v>477</v>
+      </c>
       <c r="BP6" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="BT6">
         <v>0.1</v>
@@ -7286,80 +7474,69 @@
       <c r="CU8" s="2" t="s">
         <v>461</v>
       </c>
+      <c r="DD8">
+        <v>1</v>
+      </c>
+      <c r="DG8">
+        <v>1</v>
+      </c>
+      <c r="DH8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="AG9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>449</v>
+      </c>
       <c r="AT9" s="2"/>
+      <c r="BD9">
+        <v>1</v>
+      </c>
       <c r="BV9"/>
       <c r="CL9" s="5"/>
-      <c r="CU9" s="2"/>
+      <c r="CU9" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="DD9">
+        <v>1</v>
+      </c>
+      <c r="DG9">
+        <v>1</v>
+      </c>
+      <c r="DH9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="X10" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="AJ10" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AO10" s="2"/>
-      <c r="AR10" s="2"/>
+      <c r="A10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="AG10" s="2"/>
       <c r="AT10" s="2"/>
-      <c r="AV10">
-        <v>20</v>
-      </c>
-      <c r="BD10">
-        <v>99</v>
-      </c>
-      <c r="BP10" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="BV10"/>
       <c r="CL10" s="5"/>
-      <c r="CM10" s="2"/>
-      <c r="CN10" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="CR10">
-        <v>9999</v>
-      </c>
       <c r="CU10" s="2"/>
-      <c r="DD10">
-        <v>1</v>
-      </c>
-      <c r="DG10">
-        <v>1</v>
-      </c>
-      <c r="DH10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>446</v>
@@ -7371,8 +7548,8 @@
       <c r="K11" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="X11" s="5">
-        <v>1</v>
+      <c r="Q11" s="5" t="s">
+        <v>472</v>
       </c>
       <c r="AC11">
         <v>1</v>
@@ -7385,20 +7562,20 @@
       </c>
       <c r="AO11" s="2"/>
       <c r="AR11" s="2"/>
-      <c r="AT11" s="2" t="s">
-        <v>464</v>
+      <c r="AT11" s="2"/>
+      <c r="AV11">
+        <v>20</v>
       </c>
       <c r="BD11">
         <v>99</v>
       </c>
-      <c r="BP11" s="2" t="s">
-        <v>456</v>
-      </c>
+      <c r="BO11" s="2"/>
+      <c r="BP11" s="2"/>
       <c r="BV11"/>
       <c r="CL11" s="5"/>
       <c r="CM11" s="2"/>
       <c r="CN11" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="CR11">
         <v>9999</v>
@@ -7414,482 +7591,742 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="AO12" s="2"/>
+      <c r="AR12" s="2"/>
+      <c r="AT12" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="BD12">
+        <v>99</v>
+      </c>
+      <c r="BO12" s="2"/>
+      <c r="BP12" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="BV12"/>
+      <c r="CL12" s="5"/>
+      <c r="CM12" s="2"/>
+      <c r="CN12" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="CR12">
+        <v>9999</v>
+      </c>
+      <c r="CU12" s="2"/>
+      <c r="DD12">
+        <v>1</v>
+      </c>
+      <c r="DG12">
+        <v>1</v>
+      </c>
+      <c r="DH12">
+        <v>1</v>
+      </c>
+    </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="C13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="AC13">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="AJ13" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AO13" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="AR13" s="2" t="s">
-        <v>463</v>
-      </c>
+      <c r="AG13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AO13" s="2"/>
+      <c r="AR13" s="2"/>
       <c r="AT13" s="2"/>
-      <c r="AV13">
-        <v>20</v>
-      </c>
-      <c r="BD13">
-        <v>1</v>
-      </c>
-      <c r="BP13" s="2" t="s">
-        <v>467</v>
-      </c>
+      <c r="BO13" s="2"/>
+      <c r="BP13" s="2"/>
       <c r="BV13"/>
       <c r="CL13" s="5"/>
       <c r="CM13" s="2"/>
       <c r="CN13" s="2"/>
-      <c r="CU13" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="DD13">
+      <c r="CU13" s="2"/>
+    </row>
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="DG13">
+      <c r="J14" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC14">
         <v>1</v>
       </c>
-      <c r="DH13">
+      <c r="AG14" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="AJ14" s="2"/>
+      <c r="AO14" s="2"/>
+      <c r="AR14" s="2"/>
+      <c r="AT14" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="BD14">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AJ14" s="2"/>
-      <c r="AT14" s="2"/>
-      <c r="BV14"/>
+      <c r="BO14" s="2"/>
+      <c r="BP14" s="2"/>
+      <c r="BT14">
+        <v>99999</v>
+      </c>
+      <c r="BV14">
+        <v>1</v>
+      </c>
+      <c r="BW14" s="6">
+        <v>1</v>
+      </c>
+      <c r="BX14" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="6" t="s">
+        <v>502</v>
+      </c>
       <c r="CL14" s="5"/>
       <c r="CM14" s="2"/>
-      <c r="CN14" s="2"/>
+      <c r="CN14" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="CR14">
+        <v>9999</v>
+      </c>
       <c r="CU14" s="2"/>
-    </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="AG15" s="2"/>
-      <c r="CL15" s="5"/>
-      <c r="CN15" s="2"/>
+      <c r="DD14">
+        <v>1</v>
+      </c>
+      <c r="DG14">
+        <v>1</v>
+      </c>
+      <c r="DH14">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16" s="7"/>
-      <c r="P16"/>
-      <c r="Q16"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16"/>
-      <c r="BU16" s="8"/>
-      <c r="BV16" s="8"/>
-      <c r="BW16" s="8"/>
-      <c r="BX16" s="8"/>
-      <c r="BY16" s="8"/>
-      <c r="BZ16" s="8"/>
-      <c r="CA16"/>
-    </row>
-    <row r="17" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="AR16" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="AT16" s="2"/>
+      <c r="AV16">
+        <v>20</v>
+      </c>
+      <c r="BD16">
+        <v>3</v>
+      </c>
+      <c r="BO16" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="BP16" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="BV16"/>
+      <c r="CL16" s="5"/>
+      <c r="CM16" s="2"/>
+      <c r="CN16" s="2"/>
+      <c r="CU16" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="DD16">
+        <v>1</v>
+      </c>
+      <c r="DG16">
+        <v>1</v>
+      </c>
+      <c r="DH16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17" s="7"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17"/>
       <c r="AG17" s="2"/>
+      <c r="AJ17" s="2"/>
       <c r="AT17" s="2"/>
-      <c r="BO17" s="2"/>
-      <c r="BU17" s="8"/>
-      <c r="BV17" s="8"/>
-      <c r="BW17" s="8"/>
-      <c r="BX17" s="8"/>
-      <c r="BY17" s="8"/>
-      <c r="BZ17" s="8"/>
-      <c r="CA17"/>
-      <c r="CH17" s="2"/>
-      <c r="CN17" s="3"/>
-    </row>
-    <row r="18" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18" s="7"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18"/>
-      <c r="AT18" s="2"/>
-      <c r="BU18" s="8"/>
-      <c r="BV18" s="8"/>
-      <c r="BW18" s="8"/>
-      <c r="BX18" s="8"/>
-      <c r="BY18" s="8"/>
-      <c r="BZ18" s="8"/>
-      <c r="CA18"/>
-      <c r="CH18" s="2"/>
+      <c r="BV17"/>
+      <c r="CL17" s="5"/>
+      <c r="CM17" s="2"/>
+      <c r="CN17" s="2"/>
+      <c r="CU17" s="2"/>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D18" t="s">
+        <v>488</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>483</v>
+      </c>
+      <c r="AV18">
+        <v>20</v>
+      </c>
+      <c r="BD18">
+        <v>12</v>
+      </c>
+      <c r="CL18" s="5"/>
       <c r="CN18" s="2"/>
-    </row>
-    <row r="19" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="AG19" s="2"/>
-      <c r="AY19" s="5"/>
-      <c r="BV19"/>
-      <c r="BW19"/>
-      <c r="BX19"/>
-      <c r="BY19"/>
-      <c r="BZ19"/>
-      <c r="CA19"/>
-      <c r="CB19" s="5"/>
-      <c r="CC19" s="5"/>
-      <c r="CD19" s="5"/>
-      <c r="CE19" s="5"/>
-      <c r="CF19" s="5"/>
-      <c r="CH19" s="5"/>
-      <c r="CI19" s="5"/>
-      <c r="CJ19" s="5"/>
-      <c r="CK19" s="5"/>
+      <c r="CU18" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="DD18">
+        <v>1</v>
+      </c>
+      <c r="DG18">
+        <v>1</v>
+      </c>
+      <c r="DH18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>483</v>
+      </c>
+      <c r="AV19">
+        <v>20</v>
+      </c>
+      <c r="BD19">
+        <v>99</v>
+      </c>
       <c r="CL19" s="5"/>
-      <c r="CM19" s="5"/>
-    </row>
-    <row r="20" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="CN19" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="CR19">
+        <v>1</v>
+      </c>
+      <c r="CU19" s="2"/>
+      <c r="DD19">
+        <v>1</v>
+      </c>
+      <c r="DG19">
+        <v>1</v>
+      </c>
+      <c r="DH19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
       <c r="M20"/>
       <c r="N20"/>
-      <c r="P20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20"/>
+      <c r="O20" s="7"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
       <c r="X20"/>
-      <c r="BV20"/>
-      <c r="CH20" s="2"/>
-      <c r="CN20" s="2"/>
-    </row>
-    <row r="21" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="BV21"/>
-    </row>
-    <row r="22" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="BU20" s="8"/>
+      <c r="BV20" s="8"/>
+      <c r="BW20" s="8"/>
+      <c r="BX20" s="8"/>
+      <c r="BY20" s="8"/>
+      <c r="BZ20" s="8"/>
+      <c r="CA20"/>
+    </row>
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21" s="7"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21"/>
+      <c r="AC21">
+        <v>2</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="2"/>
+      <c r="AO21" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="AT21" s="2"/>
+      <c r="AX21" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="AZ21">
+        <v>1</v>
+      </c>
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BO21" s="2"/>
+      <c r="BU21" s="8"/>
+      <c r="BV21" s="8"/>
+      <c r="BW21" s="8"/>
+      <c r="BX21" s="8"/>
+      <c r="BY21" s="8"/>
+      <c r="BZ21" s="8"/>
+      <c r="CA21"/>
+      <c r="CB21" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="CG21" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="CH21" t="s">
+        <v>496</v>
+      </c>
+      <c r="CI21" t="s">
+        <v>497</v>
+      </c>
+      <c r="CN21" s="3"/>
+    </row>
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="17"/>
+      <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="J22" s="2"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
       <c r="M22"/>
-      <c r="O22"/>
-      <c r="AG22" s="2"/>
-      <c r="BO22" s="2"/>
-      <c r="BP22" s="2"/>
+      <c r="N22"/>
+      <c r="O22" s="7"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22"/>
+      <c r="AT22" s="2"/>
+      <c r="BU22" s="8"/>
+      <c r="BV22" s="8"/>
+      <c r="BW22" s="8"/>
+      <c r="BX22" s="8"/>
+      <c r="BY22" s="8"/>
+      <c r="BZ22" s="8"/>
+      <c r="CA22"/>
+      <c r="CH22" s="2"/>
       <c r="CN22" s="2"/>
     </row>
-    <row r="23" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="J23" s="5"/>
-      <c r="M23"/>
-      <c r="O23" s="3"/>
-      <c r="P23"/>
-      <c r="Q23"/>
-      <c r="CN23" s="2"/>
-      <c r="CU23" s="2"/>
-    </row>
-    <row r="24" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="AG23" s="2"/>
+      <c r="AY23" s="5"/>
+      <c r="BV23"/>
+      <c r="BW23"/>
+      <c r="BX23"/>
+      <c r="BY23"/>
+      <c r="BZ23"/>
+      <c r="CA23"/>
+      <c r="CB23" s="5"/>
+      <c r="CC23" s="5"/>
+      <c r="CD23" s="5"/>
+      <c r="CE23" s="5"/>
+      <c r="CF23" s="5"/>
+      <c r="CH23" s="5"/>
+      <c r="CI23" s="5"/>
+      <c r="CJ23" s="5"/>
+      <c r="CK23" s="5"/>
+      <c r="CL23" s="5"/>
+      <c r="CM23" s="5"/>
+    </row>
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="AT24" s="2"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="P24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24"/>
+      <c r="X24"/>
       <c r="BV24"/>
-      <c r="CL24" s="5"/>
-      <c r="CU24" s="2"/>
-    </row>
-    <row r="25" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="O25" s="18"/>
-      <c r="AT25" s="2"/>
+      <c r="CH24" s="2"/>
+      <c r="CN24" s="2"/>
+    </row>
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="BV25"/>
-      <c r="CL25" s="5"/>
-      <c r="CN25" s="2"/>
-      <c r="CU25" s="2"/>
-    </row>
-    <row r="26" spans="1:99" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="J26" s="5"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="2"/>
+      <c r="J26" s="2"/>
       <c r="M26"/>
-      <c r="O26" s="3"/>
-      <c r="P26"/>
-      <c r="Q26"/>
+      <c r="O26"/>
+      <c r="AG26" s="2"/>
+      <c r="BO26" s="2"/>
+      <c r="BP26" s="2"/>
       <c r="CN26" s="2"/>
-      <c r="CU26" s="2"/>
-    </row>
-    <row r="27" spans="1:99" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="AG27" s="2"/>
-      <c r="AT27" s="2"/>
-      <c r="BV27"/>
-      <c r="CL27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="M27"/>
+      <c r="O27" s="3"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="CN27" s="2"/>
       <c r="CU27" s="2"/>
     </row>
-    <row r="28" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="AG28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="BV28"/>
       <c r="CL28" s="5"/>
       <c r="CU28" s="2"/>
     </row>
-    <row r="29" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="AG29" s="2"/>
+      <c r="O29" s="18"/>
       <c r="AT29" s="2"/>
       <c r="BV29"/>
       <c r="CL29" s="5"/>
+      <c r="CN29" s="2"/>
       <c r="CU29" s="2"/>
     </row>
-    <row r="30" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="J30" s="5"/>
       <c r="M30"/>
-      <c r="AY30" s="5"/>
-      <c r="BV30"/>
-      <c r="BW30"/>
-      <c r="BX30"/>
-      <c r="BY30"/>
-      <c r="BZ30"/>
-      <c r="CA30"/>
-      <c r="CB30" s="5"/>
-      <c r="CC30" s="5"/>
-      <c r="CD30" s="5"/>
-      <c r="CE30" s="5"/>
-      <c r="CF30" s="5"/>
-      <c r="CH30" s="5"/>
-      <c r="CI30" s="5"/>
-      <c r="CJ30" s="5"/>
-      <c r="CK30" s="5"/>
-      <c r="CN30" s="3"/>
-    </row>
-    <row r="31" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O30" s="3"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="CN30" s="2"/>
+      <c r="CU30" s="2"/>
+    </row>
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="7"/>
-      <c r="CH31" s="2"/>
-      <c r="CN31" s="2"/>
-    </row>
-    <row r="32" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="C31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="AG31" s="2"/>
+      <c r="AT31" s="2"/>
+      <c r="BV31"/>
+      <c r="CL31" s="5"/>
+      <c r="CU31" s="2"/>
+    </row>
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32" s="18"/>
+      <c r="Q32" s="2"/>
+      <c r="AG32" s="2"/>
+      <c r="AT32" s="2"/>
       <c r="BV32"/>
-      <c r="CI32" s="5"/>
-      <c r="CJ32" s="5"/>
+      <c r="CL32" s="5"/>
+      <c r="CU32" s="2"/>
     </row>
     <row r="33" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33" s="18"/>
-      <c r="AX33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="AG33" s="2"/>
+      <c r="AT33" s="2"/>
       <c r="BV33"/>
-      <c r="CJ33" s="5"/>
-      <c r="CM33" s="2"/>
-      <c r="CY33" s="2"/>
+      <c r="CL33" s="5"/>
+      <c r="CU33" s="2"/>
     </row>
     <row r="34" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="J34" s="2"/>
       <c r="M34"/>
-      <c r="O34" s="18"/>
-      <c r="AG34" s="2"/>
-      <c r="AO34" s="2"/>
-      <c r="BO34" s="2"/>
-      <c r="BP34" s="2"/>
-      <c r="CG34" s="2"/>
-      <c r="CM34" s="2"/>
-      <c r="CU34" s="2"/>
+      <c r="AY34" s="5"/>
+      <c r="BV34"/>
+      <c r="BW34"/>
+      <c r="BX34"/>
+      <c r="BY34"/>
+      <c r="BZ34"/>
+      <c r="CA34"/>
+      <c r="CB34" s="5"/>
+      <c r="CC34" s="5"/>
+      <c r="CD34" s="5"/>
+      <c r="CE34" s="5"/>
+      <c r="CF34" s="5"/>
+      <c r="CH34" s="5"/>
+      <c r="CI34" s="5"/>
+      <c r="CJ34" s="5"/>
+      <c r="CK34" s="5"/>
+      <c r="CN34" s="3"/>
     </row>
     <row r="35" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="C35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="M35"/>
       <c r="O35" s="18"/>
-      <c r="AG35" s="2"/>
-      <c r="AO35" s="2"/>
-      <c r="CG35" s="2"/>
+      <c r="P35" s="7"/>
+      <c r="CH35" s="2"/>
       <c r="CN35" s="2"/>
     </row>
     <row r="36" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="BU36" s="6"/>
-      <c r="CA36"/>
+      <c r="A36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36" s="18"/>
+      <c r="BV36"/>
+      <c r="CI36" s="5"/>
+      <c r="CJ36" s="5"/>
     </row>
     <row r="37" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="E37" s="2"/>
-      <c r="O37"/>
-      <c r="W37"/>
-      <c r="X37"/>
-      <c r="BO37" s="2"/>
-      <c r="BP37" s="2"/>
-      <c r="CN37" s="3"/>
+      <c r="A37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37" s="18"/>
+      <c r="AX37" s="2"/>
+      <c r="BV37"/>
+      <c r="CJ37" s="5"/>
+      <c r="CM37" s="2"/>
+      <c r="CY37" s="2"/>
     </row>
     <row r="38" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="J38" s="2"/>
       <c r="M38"/>
-      <c r="O38" s="3"/>
-      <c r="P38"/>
-      <c r="Q38"/>
-      <c r="CN38" s="3"/>
+      <c r="O38" s="18"/>
+      <c r="AG38" s="2"/>
+      <c r="AO38" s="2"/>
+      <c r="BO38" s="2"/>
+      <c r="BP38" s="2"/>
+      <c r="CG38" s="2"/>
+      <c r="CM38" s="2"/>
+      <c r="CU38" s="2"/>
     </row>
     <row r="39" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="J39" s="2"/>
       <c r="M39"/>
-      <c r="O39" s="3"/>
-      <c r="P39"/>
-      <c r="Q39"/>
-      <c r="CN39" s="3"/>
+      <c r="O39" s="18"/>
+      <c r="AG39" s="2"/>
+      <c r="AO39" s="2"/>
+      <c r="CG39" s="2"/>
+      <c r="CN39" s="2"/>
     </row>
     <row r="40" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="O40" s="3"/>
+      <c r="BU40" s="6"/>
+      <c r="CA40"/>
     </row>
     <row r="41" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="CL41" s="5"/>
+      <c r="E41" s="2"/>
+      <c r="O41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="BO41" s="2"/>
+      <c r="BP41" s="2"/>
+      <c r="CN41" s="3"/>
     </row>
     <row r="42" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="CL42" s="5"/>
+      <c r="M42"/>
+      <c r="O42" s="3"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="CN42" s="3"/>
     </row>
     <row r="43" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="AJ43" s="2"/>
-      <c r="CL43" s="5"/>
-      <c r="CU43" s="2"/>
+      <c r="M43"/>
+      <c r="O43" s="3"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="CN43" s="3"/>
     </row>
     <row r="44" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="CL44" s="5"/>
+      <c r="A44" s="2"/>
+      <c r="O44" s="3"/>
     </row>
     <row r="45" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="O45"/>
-      <c r="W45"/>
-      <c r="X45"/>
-      <c r="CN45" s="3"/>
+      <c r="A45" s="2"/>
+      <c r="CL45" s="5"/>
     </row>
     <row r="46" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="O46" s="3"/>
-      <c r="X46"/>
+      <c r="CL46" s="5"/>
     </row>
     <row r="47" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="O47" s="3"/>
-      <c r="P47"/>
-      <c r="Q47"/>
-      <c r="X47"/>
+      <c r="A47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="AJ47" s="2"/>
+      <c r="CL47" s="5"/>
+      <c r="CU47" s="2"/>
     </row>
     <row r="48" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="O48" s="3"/>
-      <c r="X48"/>
+      <c r="CL48" s="5"/>
+    </row>
+    <row r="49" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+      <c r="CN49" s="3"/>
+    </row>
+    <row r="50" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O50" s="3"/>
+      <c r="X50"/>
     </row>
     <row r="51" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="CM51" s="3"/>
-      <c r="CN51" s="3"/>
-    </row>
-    <row r="53" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="M53"/>
-      <c r="N53"/>
-      <c r="BV53"/>
-      <c r="CB53" s="9"/>
-      <c r="CI53" s="5"/>
-      <c r="CJ53" s="5"/>
-    </row>
-    <row r="54" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="BV54"/>
-      <c r="CB54" s="9"/>
-      <c r="CJ54" s="5"/>
+      <c r="O51" s="3"/>
+      <c r="P51"/>
+      <c r="Q51"/>
+      <c r="X51"/>
+    </row>
+    <row r="52" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O52" s="3"/>
+      <c r="X52"/>
     </row>
     <row r="55" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="O55"/>
-      <c r="X55"/>
       <c r="CM55" s="3"/>
+      <c r="CN55" s="3"/>
+    </row>
+    <row r="57" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="BV57"/>
+      <c r="CB57" s="9"/>
+      <c r="CI57" s="5"/>
+      <c r="CJ57" s="5"/>
     </row>
     <row r="58" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="CL58" s="5"/>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="BV58"/>
+      <c r="CB58" s="9"/>
+      <c r="CJ58" s="5"/>
     </row>
     <row r="59" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="CL59" s="5"/>
-    </row>
-    <row r="65" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL65" s="5"/>
-    </row>
-    <row r="66" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL66" s="5"/>
-    </row>
-    <row r="68" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL68" s="5"/>
+      <c r="O59"/>
+      <c r="X59"/>
+      <c r="CM59" s="3"/>
+    </row>
+    <row r="62" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="CL62" s="5"/>
+    </row>
+    <row r="63" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="CL63" s="5"/>
     </row>
     <row r="69" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL69" s="5"/>
@@ -7897,67 +8334,64 @@
     <row r="70" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL70" s="5"/>
     </row>
-    <row r="71" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL71" s="5"/>
-    </row>
     <row r="72" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV72"/>
+      <c r="CL72" s="5"/>
     </row>
     <row r="73" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV73"/>
+      <c r="CL73" s="5"/>
     </row>
     <row r="74" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV74"/>
       <c r="CL74" s="5"/>
     </row>
     <row r="75" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL75" s="5"/>
     </row>
     <row r="76" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL76" s="5"/>
+      <c r="BV76"/>
     </row>
     <row r="77" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV77"/>
     </row>
     <row r="78" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV78"/>
       <c r="CL78" s="5"/>
     </row>
+    <row r="79" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL79" s="5"/>
+    </row>
+    <row r="80" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL80" s="5"/>
+    </row>
+    <row r="81" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV81"/>
+    </row>
     <row r="82" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV82"/>
-    </row>
-    <row r="83" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL83" s="5"/>
-    </row>
-    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL91" s="5"/>
-    </row>
-    <row r="92" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL92" s="5"/>
-    </row>
-    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV93"/>
-    </row>
-    <row r="98" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV98"/>
-    </row>
-    <row r="99" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV99"/>
-      <c r="CL99" s="5"/>
-    </row>
-    <row r="100" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL100" s="5"/>
-    </row>
-    <row r="101" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL101" s="5"/>
+      <c r="CL82" s="5"/>
+    </row>
+    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV86"/>
+    </row>
+    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL87" s="5"/>
+    </row>
+    <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL95" s="5"/>
+    </row>
+    <row r="96" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL96" s="5"/>
+    </row>
+    <row r="97" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV97"/>
     </row>
     <row r="102" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL102" s="5"/>
+      <c r="BV102"/>
     </row>
     <row r="103" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV103"/>
       <c r="CL103" s="5"/>
     </row>
     <row r="104" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV104"/>
+      <c r="CL104" s="5"/>
     </row>
     <row r="105" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL105" s="5"/>
@@ -7969,10 +8403,10 @@
       <c r="CL107" s="5"/>
     </row>
     <row r="108" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL108" s="5"/>
+      <c r="BV108"/>
     </row>
     <row r="109" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV109"/>
+      <c r="CL109" s="5"/>
     </row>
     <row r="110" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL110" s="5"/>
@@ -7984,7 +8418,13 @@
       <c r="CL112" s="5"/>
     </row>
     <row r="113" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL113" s="5"/>
+      <c r="BV113"/>
+    </row>
+    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL114" s="5"/>
+    </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL115" s="5"/>
     </row>
     <row r="116" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL116" s="5"/>
@@ -7992,17 +8432,14 @@
     <row r="117" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL117" s="5"/>
     </row>
-    <row r="118" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL118" s="5"/>
-    </row>
-    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL119" s="5"/>
-    </row>
     <row r="120" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL120" s="5"/>
     </row>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL121" s="5"/>
+    </row>
     <row r="122" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV122"/>
+      <c r="CL122" s="5"/>
     </row>
     <row r="123" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL123" s="5"/>
@@ -8010,36 +8447,36 @@
     <row r="124" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL124" s="5"/>
     </row>
-    <row r="125" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL125" s="5"/>
-    </row>
     <row r="126" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL126" s="5"/>
+      <c r="BV126"/>
+    </row>
+    <row r="127" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL127" s="5"/>
+    </row>
+    <row r="128" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL128" s="5"/>
+    </row>
+    <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL129" s="5"/>
     </row>
     <row r="130" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL130" s="5"/>
     </row>
-    <row r="132" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV132"/>
-    </row>
-    <row r="133" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV133"/>
-      <c r="CL133" s="5"/>
-    </row>
     <row r="134" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL134" s="5"/>
     </row>
-    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL135" s="5"/>
-    </row>
     <row r="136" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL136" s="5"/>
+      <c r="BV136"/>
     </row>
     <row r="137" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV137"/>
       <c r="CL137" s="5"/>
     </row>
+    <row r="138" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL138" s="5"/>
+    </row>
     <row r="139" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV139"/>
+      <c r="CL139" s="5"/>
     </row>
     <row r="140" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL140" s="5"/>
@@ -8048,19 +8485,22 @@
       <c r="CL141" s="5"/>
     </row>
     <row r="143" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL143" s="5"/>
+      <c r="BV143"/>
     </row>
     <row r="144" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL144" s="5"/>
     </row>
-    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV146"/>
+    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL145" s="5"/>
     </row>
     <row r="147" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL147" s="5"/>
     </row>
+    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL148" s="5"/>
+    </row>
     <row r="150" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL150" s="5"/>
+      <c r="BV150"/>
     </row>
     <row r="151" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL151" s="5"/>
@@ -8068,82 +8508,75 @@
     <row r="154" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL154" s="5"/>
     </row>
-    <row r="156" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL156" s="5"/>
+    <row r="155" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL155" s="5"/>
     </row>
     <row r="158" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV158"/>
-    </row>
-    <row r="159" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL159" s="5"/>
+      <c r="CL158" s="5"/>
     </row>
     <row r="160" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL160" s="5"/>
     </row>
-    <row r="162" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL162" s="5"/>
-    </row>
-    <row r="163" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="162" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV162"/>
+    </row>
+    <row r="163" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL163" s="5"/>
     </row>
-    <row r="164" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="164" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL164" s="5"/>
     </row>
-    <row r="169" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL169" s="5"/>
-    </row>
-    <row r="170" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL170" s="5"/>
-    </row>
-    <row r="173" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="166" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL166" s="5"/>
+    </row>
+    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL167" s="5"/>
+    </row>
+    <row r="168" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL168" s="5"/>
+    </row>
+    <row r="173" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL173" s="5"/>
     </row>
-    <row r="174" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="174" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL174" s="5"/>
     </row>
-    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="177" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL177" s="5"/>
+    </row>
+    <row r="178" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL178" s="5"/>
     </row>
-    <row r="182" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="182" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL182" s="5"/>
     </row>
-    <row r="184" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL184" s="5"/>
-    </row>
-    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL185" s="5"/>
-    </row>
-    <row r="187" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL187" s="5"/>
-    </row>
-    <row r="188" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="186" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL186" s="5"/>
+    </row>
+    <row r="188" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL188" s="5"/>
     </row>
-    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV190"/>
-    </row>
-    <row r="191" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV191"/>
+    <row r="189" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL189" s="5"/>
+    </row>
+    <row r="191" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL191" s="5"/>
     </row>
-    <row r="192" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="192" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL192" s="5"/>
     </row>
     <row r="194" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL194" s="5"/>
-    </row>
-    <row r="203" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV203"/>
-    </row>
-    <row r="204" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV204"/>
-      <c r="CL204" s="5"/>
-    </row>
-    <row r="205" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL205" s="5"/>
-    </row>
-    <row r="206" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL206" s="5"/>
+      <c r="BV194"/>
+    </row>
+    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV195"/>
+      <c r="CL195" s="5"/>
+    </row>
+    <row r="196" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL196" s="5"/>
+    </row>
+    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL198" s="5"/>
     </row>
     <row r="207" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV207"/>
@@ -8155,6 +8588,9 @@
     <row r="209" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL209" s="5"/>
     </row>
+    <row r="210" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL210" s="5"/>
+    </row>
     <row r="211" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV211"/>
     </row>
@@ -8169,121 +8605,121 @@
       <c r="BV215"/>
     </row>
     <row r="216" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV216"/>
       <c r="CL216" s="5"/>
     </row>
+    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL217" s="5"/>
+    </row>
     <row r="219" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL219" s="5"/>
+      <c r="BV219"/>
+    </row>
+    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL220" s="5"/>
     </row>
     <row r="223" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL223" s="5"/>
     </row>
-    <row r="225" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV225"/>
-    </row>
-    <row r="226" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL226" s="5"/>
-    </row>
-    <row r="233" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV233"/>
-    </row>
-    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL234" s="5"/>
-    </row>
-    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL235" s="5"/>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL227" s="5"/>
+    </row>
+    <row r="229" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV229"/>
+    </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL230" s="5"/>
     </row>
     <row r="237" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV237"/>
     </row>
     <row r="238" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV238"/>
       <c r="CL238" s="5"/>
     </row>
     <row r="239" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL239" s="5"/>
     </row>
-    <row r="245" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV245"/>
-    </row>
-    <row r="246" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV246"/>
-      <c r="CL246" s="5"/>
-    </row>
-    <row r="247" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV247"/>
-      <c r="CL247" s="5"/>
-    </row>
-    <row r="248" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL248" s="5"/>
-    </row>
-    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV253"/>
-    </row>
-    <row r="254" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV254"/>
+    <row r="241" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV241"/>
+    </row>
+    <row r="242" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV242"/>
+      <c r="CL242" s="5"/>
+    </row>
+    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL243" s="5"/>
+    </row>
+    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV249"/>
+    </row>
+    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV250"/>
+      <c r="CL250" s="5"/>
+    </row>
+    <row r="251" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV251"/>
+      <c r="CL251" s="5"/>
+    </row>
+    <row r="252" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL252" s="5"/>
+    </row>
+    <row r="257" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV257"/>
     </row>
     <row r="258" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV258"/>
     </row>
-    <row r="259" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL259" s="5"/>
-    </row>
-    <row r="260" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV260"/>
-    </row>
-    <row r="261" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL261" s="5"/>
-    </row>
-    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV271"/>
-    </row>
-    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL272" s="5"/>
-    </row>
-    <row r="274" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV274"/>
+    <row r="262" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV262"/>
+    </row>
+    <row r="263" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL263" s="5"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV264"/>
+    </row>
+    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL265" s="5"/>
     </row>
     <row r="275" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL275" s="5"/>
-    </row>
-    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV283"/>
-    </row>
-    <row r="284" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL284" s="5"/>
+      <c r="BV275"/>
+    </row>
+    <row r="276" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL276" s="5"/>
+    </row>
+    <row r="278" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV278"/>
+    </row>
+    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL279" s="5"/>
+    </row>
+    <row r="287" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV287"/>
     </row>
     <row r="288" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV288"/>
-    </row>
-    <row r="289" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL289" s="5"/>
-    </row>
-    <row r="291" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV291"/>
+      <c r="CL288" s="5"/>
     </row>
     <row r="292" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL292" s="5"/>
-    </row>
-    <row r="308" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV308"/>
-    </row>
-    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV309"/>
-      <c r="CL309" s="5"/>
-    </row>
-    <row r="310" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV310"/>
-      <c r="CL310" s="5"/>
-    </row>
-    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV311"/>
-      <c r="CL311" s="5"/>
+      <c r="BV292"/>
+    </row>
+    <row r="293" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL293" s="5"/>
+    </row>
+    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV295"/>
+    </row>
+    <row r="296" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL296" s="5"/>
     </row>
     <row r="312" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV312"/>
     </row>
+    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV313"/>
+      <c r="CL313" s="5"/>
+    </row>
     <row r="314" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV314"/>
+      <c r="CL314" s="5"/>
     </row>
     <row r="315" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV315"/>
@@ -8291,67 +8727,67 @@
     </row>
     <row r="316" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV316"/>
-      <c r="CL316" s="5"/>
-    </row>
-    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL317" s="5"/>
+    </row>
+    <row r="318" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV318"/>
+    </row>
+    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV319"/>
+      <c r="CL319" s="5"/>
+    </row>
+    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV320"/>
+      <c r="CL320" s="5"/>
     </row>
     <row r="321" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV321"/>
-    </row>
-    <row r="322" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL322" s="5"/>
-    </row>
-    <row r="324" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV324"/>
+      <c r="CL321" s="5"/>
     </row>
     <row r="325" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV325"/>
-      <c r="CL325" s="5"/>
     </row>
     <row r="326" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV326"/>
       <c r="CL326" s="5"/>
     </row>
-    <row r="327" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL327" s="5"/>
-    </row>
-    <row r="343" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV343"/>
-    </row>
-    <row r="344" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL344" s="5"/>
-    </row>
-    <row r="352" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL352" s="5"/>
-    </row>
-    <row r="353" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL353" s="5"/>
-    </row>
-    <row r="354" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL354" s="5"/>
-    </row>
-    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL355" s="5"/>
+    <row r="328" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV328"/>
+    </row>
+    <row r="329" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV329"/>
+      <c r="CL329" s="5"/>
+    </row>
+    <row r="330" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV330"/>
+      <c r="CL330" s="5"/>
+    </row>
+    <row r="331" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL331" s="5"/>
+    </row>
+    <row r="347" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV347"/>
+    </row>
+    <row r="348" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL348" s="5"/>
     </row>
     <row r="356" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL356" s="5"/>
     </row>
+    <row r="357" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL357" s="5"/>
+    </row>
     <row r="358" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV358"/>
+      <c r="CL358" s="5"/>
     </row>
     <row r="359" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL359" s="5"/>
     </row>
     <row r="360" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV360"/>
-    </row>
-    <row r="361" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV361"/>
-      <c r="CL361" s="5"/>
+      <c r="CL360" s="5"/>
     </row>
     <row r="362" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL362" s="5"/>
+      <c r="BV362"/>
+    </row>
+    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL363" s="5"/>
     </row>
     <row r="364" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV364"/>
@@ -8361,14 +8797,18 @@
       <c r="CL365" s="5"/>
     </row>
     <row r="366" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV366"/>
       <c r="CL366" s="5"/>
     </row>
-    <row r="367" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL367" s="5"/>
+    <row r="368" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV368"/>
     </row>
     <row r="369" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV369"/>
       <c r="CL369" s="5"/>
+    </row>
+    <row r="370" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV370"/>
+      <c r="CL370" s="5"/>
     </row>
     <row r="371" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL371" s="5"/>
@@ -8376,18 +8816,12 @@
     <row r="373" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL373" s="5"/>
     </row>
-    <row r="376" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL376" s="5"/>
+    <row r="375" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL375" s="5"/>
     </row>
     <row r="377" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL377" s="5"/>
     </row>
-    <row r="378" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL378" s="5"/>
-    </row>
-    <row r="379" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL379" s="5"/>
-    </row>
     <row r="380" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL380" s="5"/>
     </row>
@@ -8395,27 +8829,30 @@
       <c r="CL381" s="5"/>
     </row>
     <row r="382" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV382"/>
+      <c r="CL382" s="5"/>
     </row>
     <row r="383" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV383"/>
       <c r="CL383" s="5"/>
     </row>
     <row r="384" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV384"/>
       <c r="CL384" s="5"/>
     </row>
     <row r="385" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL385" s="5"/>
     </row>
     <row r="386" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL386" s="5"/>
+      <c r="BV386"/>
     </row>
     <row r="387" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV387"/>
       <c r="CL387" s="5"/>
     </row>
     <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV388"/>
       <c r="CL388" s="5"/>
+    </row>
+    <row r="389" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL389" s="5"/>
     </row>
     <row r="390" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL390" s="5"/>
@@ -8424,35 +8861,30 @@
       <c r="CL391" s="5"/>
     </row>
     <row r="392" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV392"/>
-    </row>
-    <row r="393" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV393"/>
-      <c r="CL393" s="5"/>
+      <c r="CL392" s="5"/>
     </row>
     <row r="394" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV394"/>
       <c r="CL394" s="5"/>
     </row>
     <row r="395" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL395" s="5"/>
     </row>
     <row r="396" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL396" s="5"/>
+      <c r="BV396"/>
+    </row>
+    <row r="397" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV397"/>
+      <c r="CL397" s="5"/>
     </row>
     <row r="398" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV398"/>
       <c r="CL398" s="5"/>
     </row>
     <row r="399" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL399" s="5"/>
     </row>
     <row r="400" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV400"/>
       <c r="CL400" s="5"/>
-    </row>
-    <row r="401" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV401"/>
-      <c r="CL401" s="5"/>
     </row>
     <row r="402" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL402" s="5"/>
@@ -8461,10 +8893,14 @@
       <c r="CL403" s="5"/>
     </row>
     <row r="404" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV404"/>
       <c r="CL404" s="5"/>
     </row>
+    <row r="405" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV405"/>
+      <c r="CL405" s="5"/>
+    </row>
     <row r="406" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV406"/>
       <c r="CL406" s="5"/>
     </row>
     <row r="407" spans="74:90" x14ac:dyDescent="0.25">
@@ -8478,55 +8914,56 @@
       <c r="CL410" s="5"/>
     </row>
     <row r="411" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV411"/>
       <c r="CL411" s="5"/>
     </row>
     <row r="412" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL412" s="5"/>
     </row>
     <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV414"/>
       <c r="CL414" s="5"/>
+    </row>
+    <row r="415" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV415"/>
+      <c r="CL415" s="5"/>
     </row>
     <row r="416" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL416" s="5"/>
     </row>
-    <row r="419" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL419" s="5"/>
+    <row r="418" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL418" s="5"/>
     </row>
     <row r="420" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL420" s="5"/>
     </row>
+    <row r="423" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL423" s="5"/>
+    </row>
     <row r="424" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV424"/>
-    </row>
-    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV425"/>
-      <c r="CL425" s="5"/>
-    </row>
-    <row r="426" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV426"/>
-      <c r="CL426" s="5"/>
-    </row>
-    <row r="427" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL427" s="5"/>
+      <c r="CL424" s="5"/>
     </row>
     <row r="428" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL428" s="5"/>
+      <c r="BV428"/>
     </row>
     <row r="429" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV429"/>
+      <c r="CL429" s="5"/>
     </row>
     <row r="430" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV430"/>
       <c r="CL430" s="5"/>
+    </row>
+    <row r="431" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL431" s="5"/>
     </row>
     <row r="432" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL432" s="5"/>
     </row>
     <row r="433" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL433" s="5"/>
-    </row>
-    <row r="435" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL435" s="5"/>
+      <c r="BV433"/>
+    </row>
+    <row r="434" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL434" s="5"/>
     </row>
     <row r="436" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL436" s="5"/>
@@ -8534,9 +8971,6 @@
     <row r="437" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL437" s="5"/>
     </row>
-    <row r="438" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL438" s="5"/>
-    </row>
     <row r="439" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL439" s="5"/>
     </row>
@@ -8546,8 +8980,11 @@
     <row r="441" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL441" s="5"/>
     </row>
+    <row r="442" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL442" s="5"/>
+    </row>
     <row r="443" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV443"/>
+      <c r="CL443" s="5"/>
     </row>
     <row r="444" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL444" s="5"/>
@@ -8555,78 +8992,71 @@
     <row r="445" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL445" s="5"/>
     </row>
-    <row r="478" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU478" s="10"/>
-      <c r="BV478" s="11"/>
-    </row>
-    <row r="479" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H479" s="10"/>
-      <c r="CL479" s="10"/>
-    </row>
-    <row r="485" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV485"/>
-    </row>
-    <row r="486" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV486"/>
-      <c r="CL486" s="5"/>
-    </row>
-    <row r="487" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV487"/>
-      <c r="CL487" s="5"/>
-    </row>
-    <row r="488" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL488" s="5"/>
-    </row>
-    <row r="505" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV505"/>
-    </row>
-    <row r="506" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL506" s="5"/>
-    </row>
-    <row r="538" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV538"/>
-    </row>
-    <row r="539" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV539"/>
-      <c r="CL539" s="5"/>
-    </row>
-    <row r="540" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL540" s="5"/>
-    </row>
-    <row r="556" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV556"/>
-    </row>
-    <row r="557" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL557" s="5"/>
-    </row>
-    <row r="563" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV563"/>
-    </row>
-    <row r="564" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV564"/>
-      <c r="CL564" s="5"/>
-    </row>
-    <row r="565" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL565" s="5"/>
-    </row>
-    <row r="570" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV570"/>
-    </row>
-    <row r="571" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV571"/>
-      <c r="CL571" s="5"/>
-    </row>
-    <row r="572" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV572"/>
-      <c r="CL572" s="5"/>
-    </row>
-    <row r="573" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV573"/>
-      <c r="CL573" s="5"/>
+    <row r="447" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV447"/>
+    </row>
+    <row r="448" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL448" s="5"/>
+    </row>
+    <row r="449" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL449" s="5"/>
+    </row>
+    <row r="482" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU482" s="10"/>
+      <c r="BV482" s="11"/>
+    </row>
+    <row r="483" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H483" s="10"/>
+      <c r="CL483" s="10"/>
+    </row>
+    <row r="489" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV489"/>
+    </row>
+    <row r="490" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV490"/>
+      <c r="CL490" s="5"/>
+    </row>
+    <row r="491" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV491"/>
+      <c r="CL491" s="5"/>
+    </row>
+    <row r="492" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL492" s="5"/>
+    </row>
+    <row r="509" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV509"/>
+    </row>
+    <row r="510" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL510" s="5"/>
+    </row>
+    <row r="542" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV542"/>
+    </row>
+    <row r="543" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV543"/>
+      <c r="CL543" s="5"/>
+    </row>
+    <row r="544" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL544" s="5"/>
+    </row>
+    <row r="560" spans="74:74" x14ac:dyDescent="0.25">
+      <c r="BV560"/>
+    </row>
+    <row r="561" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL561" s="5"/>
+    </row>
+    <row r="567" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV567"/>
+    </row>
+    <row r="568" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV568"/>
+      <c r="CL568" s="5"/>
+    </row>
+    <row r="569" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL569" s="5"/>
     </row>
     <row r="574" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV574"/>
-      <c r="CL574" s="5"/>
     </row>
     <row r="575" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV575"/>
@@ -8673,52 +9103,52 @@
       <c r="CL585" s="5"/>
     </row>
     <row r="586" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV586"/>
       <c r="CL586" s="5"/>
     </row>
+    <row r="587" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV587"/>
+      <c r="CL587" s="5"/>
+    </row>
+    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV588"/>
+      <c r="CL588" s="5"/>
+    </row>
+    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV589"/>
+      <c r="CL589" s="5"/>
+    </row>
     <row r="590" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV590"/>
-    </row>
-    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV591"/>
-      <c r="CL591" s="5"/>
-    </row>
-    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL592" s="5"/>
-    </row>
-    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV593"/>
+      <c r="CL590" s="5"/>
     </row>
     <row r="594" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL594" s="5"/>
+      <c r="BV594"/>
+    </row>
+    <row r="595" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV595"/>
+      <c r="CL595" s="5"/>
+    </row>
+    <row r="596" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL596" s="5"/>
     </row>
     <row r="597" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV597"/>
     </row>
     <row r="598" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV598"/>
       <c r="CL598" s="5"/>
     </row>
-    <row r="599" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL599" s="5"/>
-    </row>
-    <row r="630" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV630"/>
-    </row>
-    <row r="631" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV631"/>
-      <c r="CL631" s="5"/>
-    </row>
-    <row r="632" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV632"/>
-      <c r="CL632" s="5"/>
-    </row>
-    <row r="633" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV633"/>
-      <c r="CL633" s="5"/>
+    <row r="601" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV601"/>
+    </row>
+    <row r="602" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV602"/>
+      <c r="CL602" s="5"/>
+    </row>
+    <row r="603" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL603" s="5"/>
     </row>
     <row r="634" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV634"/>
-      <c r="CL634" s="5"/>
     </row>
     <row r="635" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV635"/>
@@ -8733,64 +9163,70 @@
       <c r="CL637" s="5"/>
     </row>
     <row r="638" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV638"/>
       <c r="CL638" s="5"/>
+    </row>
+    <row r="639" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV639"/>
+      <c r="CL639" s="5"/>
     </row>
     <row r="640" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV640"/>
+      <c r="CL640" s="5"/>
     </row>
     <row r="641" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV641"/>
       <c r="CL641" s="5"/>
     </row>
+    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL642" s="5"/>
+    </row>
+    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV644"/>
+    </row>
     <row r="645" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV645"/>
-    </row>
-    <row r="646" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL646" s="5"/>
+      <c r="CL645" s="5"/>
     </row>
     <row r="649" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV649"/>
     </row>
     <row r="650" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV650"/>
       <c r="CL650" s="5"/>
     </row>
-    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV651"/>
-      <c r="CL651" s="5"/>
-    </row>
-    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV652"/>
-      <c r="CL652" s="5"/>
-    </row>
     <row r="653" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL653" s="5"/>
-    </row>
-    <row r="660" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV660"/>
-    </row>
-    <row r="661" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL661" s="5"/>
+      <c r="BV653"/>
+    </row>
+    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV654"/>
+      <c r="CL654" s="5"/>
+    </row>
+    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV655"/>
+      <c r="CL655" s="5"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV656"/>
+      <c r="CL656" s="5"/>
+    </row>
+    <row r="657" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL657" s="5"/>
     </row>
     <row r="664" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV664"/>
     </row>
     <row r="665" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV665"/>
       <c r="CL665" s="5"/>
     </row>
-    <row r="666" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV666"/>
-      <c r="CL666" s="5"/>
-    </row>
-    <row r="667" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV667"/>
-      <c r="CL667" s="5"/>
-    </row>
     <row r="668" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL668" s="5"/>
+      <c r="BV668"/>
+    </row>
+    <row r="669" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV669"/>
+      <c r="CL669" s="5"/>
     </row>
     <row r="670" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV670"/>
+      <c r="CL670" s="5"/>
     </row>
     <row r="671" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV671"/>
@@ -8799,74 +9235,68 @@
     <row r="672" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL672" s="5"/>
     </row>
-    <row r="673" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL673">
+    <row r="674" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV674"/>
+    </row>
+    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV675"/>
+      <c r="CL675" s="5"/>
+    </row>
+    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL676" s="5"/>
+    </row>
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL677">
         <v>0.15</v>
       </c>
     </row>
-    <row r="675" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL675">
+    <row r="679" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL679">
         <v>0.2</v>
       </c>
     </row>
-    <row r="676" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL676">
+    <row r="680" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL680">
         <v>0.1</v>
       </c>
     </row>
-    <row r="678" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL678">
+    <row r="682" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL682">
         <v>0.2</v>
       </c>
     </row>
-    <row r="685" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL685">
+    <row r="689" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL689">
         <v>1</v>
-      </c>
-    </row>
-    <row r="687" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL687">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="688" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL688">
-        <v>0.6</v>
       </c>
     </row>
     <row r="691" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL691">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="692" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL692">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="695" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL695">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="696" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL696">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="693" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL693">
+    <row r="697" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL697">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="696" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV696"/>
-    </row>
-    <row r="697" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV697"/>
-      <c r="CL697" s="5"/>
-    </row>
-    <row r="698" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV698"/>
-      <c r="CL698" s="5"/>
-    </row>
-    <row r="699" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV699"/>
-      <c r="CL699" s="5"/>
     </row>
     <row r="700" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV700"/>
-      <c r="CL700" s="5"/>
     </row>
     <row r="701" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV701"/>
@@ -8885,32 +9315,32 @@
       <c r="CL704" s="5"/>
     </row>
     <row r="705" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV705"/>
       <c r="CL705" s="5"/>
     </row>
     <row r="706" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV706"/>
+      <c r="CL706" s="5"/>
     </row>
     <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV707"/>
       <c r="CL707" s="5"/>
     </row>
-    <row r="716" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV716"/>
-    </row>
-    <row r="717" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV717"/>
-      <c r="CL717" s="5"/>
-    </row>
-    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV718"/>
-      <c r="CL718" s="5"/>
-    </row>
-    <row r="719" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV719"/>
-      <c r="CL719" s="5"/>
+    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV708"/>
+      <c r="CL708" s="5"/>
+    </row>
+    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL709" s="5"/>
+    </row>
+    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV710"/>
+    </row>
+    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL711" s="5"/>
     </row>
     <row r="720" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV720"/>
-      <c r="CL720" s="5"/>
     </row>
     <row r="721" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV721"/>
@@ -8925,132 +9355,132 @@
       <c r="CL723" s="5"/>
     </row>
     <row r="724" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV724"/>
       <c r="CL724" s="5"/>
     </row>
     <row r="725" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV725"/>
+      <c r="CL725" s="5"/>
     </row>
     <row r="726" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV726"/>
       <c r="CL726" s="5"/>
     </row>
-    <row r="731" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV731"/>
-    </row>
-    <row r="732" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV732"/>
-      <c r="CL732" s="5"/>
-    </row>
-    <row r="733" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL733" s="5"/>
-    </row>
-    <row r="734" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV734"/>
+    <row r="727" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
+      <c r="CL727" s="5"/>
+    </row>
+    <row r="728" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL728" s="5"/>
+    </row>
+    <row r="729" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV729"/>
+    </row>
+    <row r="730" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL730" s="5"/>
     </row>
     <row r="735" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV735"/>
-      <c r="CL735" s="5"/>
     </row>
     <row r="736" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV736"/>
       <c r="CL736" s="5"/>
     </row>
-    <row r="737" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV737"/>
-    </row>
-    <row r="738" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="737" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL737" s="5"/>
+    </row>
+    <row r="738" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV738"/>
-      <c r="CL738" s="5"/>
-    </row>
-    <row r="739" spans="8:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="739" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV739"/>
       <c r="CL739" s="5"/>
     </row>
-    <row r="740" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV740"/>
+    <row r="740" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL740" s="5"/>
     </row>
-    <row r="741" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL741" s="5"/>
-    </row>
-    <row r="745" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV745"/>
-    </row>
-    <row r="746" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV746"/>
-      <c r="CL746" s="5"/>
-    </row>
-    <row r="747" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV747"/>
-      <c r="CL747" s="5"/>
-    </row>
-    <row r="748" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL748" s="5"/>
-    </row>
-    <row r="749" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="741" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV741"/>
+    </row>
+    <row r="742" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV742"/>
+      <c r="CL742" s="5"/>
+    </row>
+    <row r="743" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV743"/>
+      <c r="CL743" s="5"/>
+    </row>
+    <row r="744" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV744"/>
+      <c r="CL744" s="5"/>
+    </row>
+    <row r="745" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL745" s="5"/>
+    </row>
+    <row r="749" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV749"/>
     </row>
-    <row r="750" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="750" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV750"/>
       <c r="CL750" s="5"/>
     </row>
-    <row r="751" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU751" s="10"/>
-      <c r="BV751" s="11"/>
-    </row>
-    <row r="752" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H752" s="10"/>
-      <c r="CL752" s="10"/>
-    </row>
-    <row r="769" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV769"/>
-    </row>
-    <row r="770" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV770"/>
-      <c r="CL770" s="5"/>
-    </row>
-    <row r="771" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV771"/>
-      <c r="CL771" s="5"/>
-    </row>
-    <row r="772" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV772"/>
-      <c r="CL772" s="5"/>
+    <row r="751" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV751"/>
+      <c r="CL751" s="5"/>
+    </row>
+    <row r="752" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL752" s="5"/>
+    </row>
+    <row r="753" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV753"/>
+    </row>
+    <row r="754" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL754" s="5"/>
+    </row>
+    <row r="755" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU755" s="10"/>
+      <c r="BV755" s="11"/>
+    </row>
+    <row r="756" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H756" s="10"/>
+      <c r="CL756" s="10"/>
     </row>
     <row r="773" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL773" s="5"/>
+      <c r="BV773"/>
     </row>
     <row r="774" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV774"/>
+      <c r="CL774" s="5"/>
     </row>
     <row r="775" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV775"/>
       <c r="CL775" s="5"/>
     </row>
     <row r="776" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU776" s="10"/>
-      <c r="BV776" s="11"/>
+      <c r="BV776"/>
       <c r="CL776" s="5"/>
     </row>
     <row r="777" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H777" s="10"/>
-      <c r="CL777" s="10"/>
+      <c r="CL777" s="5"/>
+    </row>
+    <row r="778" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV778"/>
+    </row>
+    <row r="779" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV779"/>
+      <c r="CL779" s="5"/>
     </row>
     <row r="780" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV780"/>
+      <c r="BU780" s="10"/>
+      <c r="BV780" s="11"/>
+      <c r="CL780" s="5"/>
     </row>
     <row r="781" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV781"/>
-      <c r="CL781" s="5"/>
-    </row>
-    <row r="782" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV782"/>
-      <c r="CL782" s="5"/>
-    </row>
-    <row r="783" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV783"/>
-      <c r="CL783" s="5"/>
+      <c r="H781" s="10"/>
+      <c r="CL781" s="10"/>
     </row>
     <row r="784" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV784"/>
-      <c r="CL784" s="5"/>
     </row>
     <row r="785" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV785"/>
@@ -9065,36 +9495,38 @@
       <c r="CL787" s="5"/>
     </row>
     <row r="788" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV788"/>
       <c r="CL788" s="5"/>
+    </row>
+    <row r="789" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV789"/>
+      <c r="CL789" s="5"/>
     </row>
     <row r="790" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV790"/>
+      <c r="CL790" s="5"/>
     </row>
     <row r="791" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV791"/>
       <c r="CL791" s="5"/>
     </row>
     <row r="792" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV792"/>
       <c r="CL792" s="5"/>
-    </row>
-    <row r="793" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV793"/>
-      <c r="CL793" s="5"/>
     </row>
     <row r="794" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV794"/>
-      <c r="CL794" s="5"/>
     </row>
     <row r="795" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV795"/>
       <c r="CL795" s="5"/>
     </row>
     <row r="796" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV796"/>
       <c r="CL796" s="5"/>
     </row>
     <row r="797" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV797"/>
+      <c r="CL797" s="5"/>
     </row>
     <row r="798" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV798"/>
@@ -9105,12 +9537,10 @@
       <c r="CL799" s="5"/>
     </row>
     <row r="800" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV800"/>
       <c r="CL800" s="5"/>
     </row>
     <row r="801" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV801"/>
-      <c r="CL801" s="5"/>
     </row>
     <row r="802" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV802"/>
@@ -9213,10 +9643,12 @@
       <c r="CL826" s="5"/>
     </row>
     <row r="827" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV827"/>
       <c r="CL827" s="5"/>
     </row>
     <row r="828" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV828"/>
+      <c r="CL828" s="5"/>
     </row>
     <row r="829" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV829"/>
@@ -9228,6 +9660,20 @@
     </row>
     <row r="831" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL831" s="5"/>
+    </row>
+    <row r="832" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV832"/>
+    </row>
+    <row r="833" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV833"/>
+      <c r="CL833" s="5"/>
+    </row>
+    <row r="834" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV834"/>
+      <c r="CL834" s="5"/>
+    </row>
+    <row r="835" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL835" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -9408,31 +9854,34 @@
         <v>462</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q8" s="2"/>
     </row>

--- a/Excel/Diy优胜/恶堕凛视.xlsx
+++ b/Excel/Diy优胜/恶堕凛视.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F10D07-957A-4A6B-9FEE-202BEE93DC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A3A593-5892-4BEE-8FC2-5852A2F345A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="511">
   <si>
     <t>Id</t>
   </si>
@@ -1889,6 +1889,32 @@
   </si>
   <si>
     <t>即死</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>刹那兴衰</t>
+  </si>
+  <si>
+    <t>刹那兴衰</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：攻击范围内的双方弹道移动速度大幅降低
+可以在兴盛状态与衰败状态之间切换：
+兴盛状态：双方弹道每在自身攻击范围内停留0.2秒伤害+3%（至多+90%）。
+衰败状态：双方弹道每在自身攻击范围内停留0.2秒伤害-3%（至多-90%）。</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通buff</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>衰败</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>一技能被动效果</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1896,7 +1922,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2019,6 +2045,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2057,7 +2092,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2114,6 +2149,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7352,17 +7399,12 @@
       <c r="E6" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>431</v>
-      </c>
+      <c r="J6" s="2"/>
       <c r="K6" s="5" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="P6" s="7"/>
       <c r="X6" s="5">
@@ -7373,24 +7415,6 @@
       </c>
       <c r="BP6" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="BT6">
-        <v>0.1</v>
-      </c>
-      <c r="BU6">
-        <v>1</v>
-      </c>
-      <c r="BV6" s="6">
-        <v>0</v>
-      </c>
-      <c r="BW6" s="6">
-        <v>5</v>
-      </c>
-      <c r="BX6" s="6">
-        <v>1</v>
-      </c>
-      <c r="BY6" s="6" t="s">
-        <v>430</v>
       </c>
       <c r="CH6" s="2"/>
       <c r="CN6" s="2"/>
@@ -8025,31 +8049,86 @@
       <c r="CH22" s="2"/>
       <c r="CN22" s="2"/>
     </row>
-    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="AG23" s="2"/>
-      <c r="AY23" s="5"/>
-      <c r="BV23"/>
-      <c r="BW23"/>
-      <c r="BX23"/>
-      <c r="BY23"/>
-      <c r="BZ23"/>
-      <c r="CA23"/>
-      <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
-      <c r="CD23" s="5"/>
-      <c r="CE23" s="5"/>
-      <c r="CF23" s="5"/>
-      <c r="CH23" s="5"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="5"/>
-      <c r="CK23" s="5"/>
-      <c r="CL23" s="5"/>
-      <c r="CM23" s="5"/>
+    <row r="23" spans="1:112" s="21" customFormat="1" ht="15.45" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="G23" s="21">
+        <v>3</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="AG23" s="20"/>
+      <c r="AY23" s="23"/>
+      <c r="BO23" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="BP23" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="BT23" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="BV23" s="21">
+        <v>0</v>
+      </c>
+      <c r="BW23" s="21">
+        <v>6</v>
+      </c>
+      <c r="BX23" s="21">
+        <v>1</v>
+      </c>
+      <c r="BY23" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="CB23" s="23"/>
+      <c r="CC23" s="23"/>
+      <c r="CD23" s="23"/>
+      <c r="CE23" s="23"/>
+      <c r="CF23" s="23"/>
+      <c r="CH23" s="23"/>
+      <c r="CI23" s="23"/>
+      <c r="CJ23" s="23"/>
+      <c r="CK23" s="23"/>
+      <c r="CL23" s="23"/>
+      <c r="CM23" s="23"/>
+      <c r="CN23" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="CR23" s="21">
+        <v>9999</v>
+      </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
+      <c r="A24" s="20" t="s">
+        <v>510</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="17"/>
       <c r="E24" s="2"/>
@@ -9890,8 +9969,18 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
       <c r="Q10" s="2"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">

--- a/Excel/Diy优胜/恶堕凛视.xlsx
+++ b/Excel/Diy优胜/恶堕凛视.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A3A593-5892-4BEE-8FC2-5852A2F345A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B57FC7-5F43-4CA5-B657-5265EA7A41AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="510">
   <si>
     <t>Id</t>
   </si>
@@ -1893,16 +1893,6 @@
   </si>
   <si>
     <t>刹那兴衰</t>
-  </si>
-  <si>
-    <t>刹那兴衰</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>被动：攻击范围内的双方弹道移动速度大幅降低
-可以在兴盛状态与衰败状态之间切换：
-兴盛状态：双方弹道每在自身攻击范围内停留0.2秒伤害+3%（至多+90%）。
-衰败状态：双方弹道每在自身攻击范围内停留0.2秒伤害-3%（至多-90%）。</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -1915,6 +1905,10 @@
   </si>
   <si>
     <t>一技能被动效果</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动：攻击范围内的双方弹道移动速度大幅降低\n可以在兴盛状态与衰败状态之间切换：\n兴盛状态：双方弹道每在自身攻击范围内停留0.2秒伤害+3%（至多+90%）。\n衰败状态：双方弹道每在自身攻击范围内停留0.2秒伤害-3%（至多-90%）。</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1922,7 +1916,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2045,15 +2039,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2092,7 +2077,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2149,18 +2134,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8049,85 +8022,74 @@
       <c r="CH22" s="2"/>
       <c r="CN22" s="2"/>
     </row>
-    <row r="23" spans="1:112" s="21" customFormat="1" ht="15.45" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>506</v>
-      </c>
-      <c r="C23" s="20" t="s">
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="AG23" s="2"/>
+      <c r="AY23" s="5"/>
+      <c r="BO23" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="BP23" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="BT23">
+        <v>0.1</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>6</v>
+      </c>
+      <c r="BX23">
+        <v>1</v>
+      </c>
+      <c r="BY23" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="BZ23"/>
+      <c r="CA23"/>
+      <c r="CB23" s="5"/>
+      <c r="CC23" s="5"/>
+      <c r="CD23" s="5"/>
+      <c r="CE23" s="5"/>
+      <c r="CF23" s="5"/>
+      <c r="CH23" s="5"/>
+      <c r="CI23" s="5"/>
+      <c r="CJ23" s="5"/>
+      <c r="CK23" s="5"/>
+      <c r="CL23" s="5"/>
+      <c r="CM23" s="5"/>
+      <c r="CN23" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="G23" s="21">
-        <v>3</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>431</v>
-      </c>
-      <c r="K23" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="AG23" s="20"/>
-      <c r="AY23" s="23"/>
-      <c r="BO23" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="BP23" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="BT23" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="BV23" s="21">
-        <v>0</v>
-      </c>
-      <c r="BW23" s="21">
-        <v>6</v>
-      </c>
-      <c r="BX23" s="21">
-        <v>1</v>
-      </c>
-      <c r="BY23" s="20" t="s">
-        <v>430</v>
-      </c>
-      <c r="CB23" s="23"/>
-      <c r="CC23" s="23"/>
-      <c r="CD23" s="23"/>
-      <c r="CE23" s="23"/>
-      <c r="CF23" s="23"/>
-      <c r="CH23" s="23"/>
-      <c r="CI23" s="23"/>
-      <c r="CJ23" s="23"/>
-      <c r="CK23" s="23"/>
-      <c r="CL23" s="23"/>
-      <c r="CM23" s="23"/>
-      <c r="CN23" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="CR23" s="21">
+      <c r="CR23">
         <v>9999</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>510</v>
+      <c r="A24" s="2" t="s">
+        <v>508</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="17"/>
@@ -9970,10 +9932,10 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H10">
         <v>1</v>

--- a/Excel/Diy优胜/恶堕凛视.xlsx
+++ b/Excel/Diy优胜/恶堕凛视.xlsx
@@ -24,9 +24,9 @@
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="OLE_LINK2" localSheetId="2">SkillData!$E$21</definedName>
+    <definedName name="OLE_LINK2" localSheetId="2">'SkillData'!$E$21</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
   <si>
     <t>Id</t>
   </si>
@@ -316,6 +316,9 @@
     <t>UnitData[]</t>
   </si>
   <si>
+    <t>恶堕凛视</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -373,6 +376,9 @@
     <t>部署策略</t>
   </si>
   <si>
+    <t>可部署上限</t>
+  </si>
+  <si>
     <t>仇恨等级</t>
   </si>
   <si>
@@ -529,6 +535,9 @@
     <t>RedeployPolicy</t>
   </si>
   <si>
+    <t>BuildCountLimit</t>
+  </si>
+  <si>
     <t>Hatred</t>
   </si>
   <si>
@@ -679,9 +688,6 @@
     <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
   </si>
   <si>
-    <t>恶堕凛视</t>
-  </si>
-  <si>
     <t>干员</t>
   </si>
   <si>
@@ -1759,6 +1765,9 @@
     <t>MapHp</t>
   </si>
   <si>
+    <t>UnitTypeEnum[]</t>
+  </si>
+  <si>
     <t>仅单面</t>
   </si>
   <si>
@@ -1805,20 +1814,14 @@
   </si>
   <si>
     <t>BackSkelPath</t>
-  </si>
-  <si>
-    <t>UnitTypeEnum[]</t>
-  </si>
-  <si>
-    <t>恶堕凛视</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1830,27 +1833,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1880,19 +1862,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2197,978 +2179,1226 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1"/>
+    <col min="1" max="2" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BT7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
-    <col min="8" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
-    <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
-    <col min="27" max="28" width="9" customWidth="1"/>
-    <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="9.75" customWidth="1"/>
-    <col min="33" max="33" width="7.83203125" customWidth="1"/>
-    <col min="34" max="34" width="15.83203125" customWidth="1"/>
-    <col min="35" max="35" width="13.83203125" customWidth="1"/>
-    <col min="36" max="36" width="63.75" customWidth="1"/>
-    <col min="37" max="37" width="20.1640625" customWidth="1"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1"/>
-    <col min="39" max="42" width="9" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="44" max="49" width="9" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="54" max="55" width="9" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="60" max="63" width="9" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6" customWidth="1" style="2"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1" style="2"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="4" customWidth="1" style="2"/>
+    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
+    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
+    <col min="27" max="27" width="9" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="8" customWidth="1" style="2"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="9" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="63.75" customWidth="1" style="2"/>
+    <col min="38" max="38" width="20.1640625" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="9" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
+    <col min="55" max="55" width="9" customWidth="1" style="2"/>
+    <col min="56" max="56" width="9" customWidth="1" style="2"/>
+    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
+    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8" customWidth="1" style="2"/>
+    <col min="61" max="61" width="9" customWidth="1" style="2"/>
+    <col min="62" max="62" width="9" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
+    <col min="66" max="66" width="14" customWidth="1" style="2"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="2"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BJ4" s="2"/>
+      <c r="BK4" s="2"/>
+      <c r="BL4" s="2"/>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>90</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1400</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
+        <v>650</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2">
+        <v>125</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2">
+        <v>25</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2">
+        <v>14</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="2">
+        <v>70</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="AJ5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AM5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AP5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2"/>
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BI5" s="2">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>44</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>46</v>
+      <c r="BJ5" s="2"/>
+      <c r="BK5" s="2"/>
+      <c r="BL5" s="2"/>
+      <c r="BM5" s="2"/>
+      <c r="BN5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BP5" s="2"/>
+      <c r="BQ5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BT5" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>90</v>
+      </c>
+      <c r="K6" s="2">
+        <v>100</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" t="s">
-        <v>58</v>
-      </c>
-      <c r="P2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" t="s">
-        <v>64</v>
-      </c>
-      <c r="V2" t="s">
-        <v>65</v>
-      </c>
-      <c r="W2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AR6" s="2"/>
+      <c r="AS6" s="2"/>
+      <c r="AT6" s="2"/>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2"/>
+      <c r="AW6" s="2"/>
+      <c r="AX6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY6" s="2"/>
+      <c r="AZ6" s="2"/>
+      <c r="BA6" s="2"/>
+      <c r="BB6" s="2"/>
+      <c r="BC6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BD6" s="2"/>
+      <c r="BE6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BI6" s="2">
+        <v>6</v>
+      </c>
+      <c r="BJ6" s="2"/>
+      <c r="BK6" s="2"/>
+      <c r="BL6" s="2"/>
+      <c r="BM6" s="2"/>
+      <c r="BN6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BP6" s="2"/>
+      <c r="BQ6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BS6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BT6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
         <v>90</v>
       </c>
-      <c r="AV2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" t="s">
+      <c r="K7" s="2">
         <v>100</v>
       </c>
-      <c r="BF2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" t="s">
-        <v>117</v>
-      </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
-        <v>117</v>
-      </c>
-      <c r="P3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>117</v>
-      </c>
-      <c r="R3" t="s">
-        <v>117</v>
-      </c>
-      <c r="S3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>90</v>
-      </c>
-      <c r="K5">
-        <v>1400</v>
-      </c>
-      <c r="M5">
-        <v>650</v>
-      </c>
-      <c r="O5">
-        <v>125</v>
-      </c>
-      <c r="Q5">
-        <v>25</v>
-      </c>
-      <c r="S5">
-        <v>14</v>
-      </c>
-      <c r="U5">
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK7" s="2"/>
+      <c r="AL7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM7" s="2">
+        <v>3</v>
+      </c>
+      <c r="AN7" s="2"/>
+      <c r="AO7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="2">
         <v>0.5</v>
       </c>
-      <c r="V5">
-        <v>70</v>
-      </c>
-      <c r="Y5">
-        <v>0.05</v>
-      </c>
-      <c r="Z5">
-        <v>1.9</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>129</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO5">
-        <v>1</v>
-      </c>
-      <c r="AP5">
-        <v>0.5</v>
-      </c>
-      <c r="AW5">
+      <c r="AR7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="2"/>
+      <c r="AT7" s="2"/>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2"/>
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="2">
         <v>0.25</v>
       </c>
-      <c r="BB5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BE5" t="s">
+      <c r="AY7" s="2"/>
+      <c r="AZ7" s="2"/>
+      <c r="BA7" s="2"/>
+      <c r="BB7" s="2"/>
+      <c r="BC7" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BD7" s="2"/>
+      <c r="BE7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BF7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="BH5">
+      <c r="BG7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BI7" s="2">
         <v>6</v>
       </c>
-      <c r="BM5" t="s">
-        <v>137</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>139</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6">
-        <v>0.5</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>90</v>
-      </c>
-      <c r="K6">
-        <v>100</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0.05</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>142</v>
-      </c>
-      <c r="AL6">
-        <v>3</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0.5</v>
-      </c>
-      <c r="AW6">
-        <v>0.25</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>132</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>133</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BH6">
-        <v>6</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>138</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0.05</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>146</v>
-      </c>
-      <c r="AL7">
-        <v>3</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0.5</v>
-      </c>
-      <c r="AQ7">
-        <v>1</v>
-      </c>
-      <c r="AW7">
-        <v>0.25</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>132</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>133</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>136</v>
-      </c>
-      <c r="BH7">
-        <v>6</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>148</v>
-      </c>
+      <c r="BJ7" s="2"/>
+      <c r="BK7" s="2"/>
+      <c r="BL7" s="2"/>
+      <c r="BM7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN7" s="2"/>
+      <c r="BO7" s="2"/>
+      <c r="BP7" s="2"/>
+      <c r="BQ7" s="2"/>
+      <c r="BR7" s="2"/>
+      <c r="BS7" s="2"/>
+      <c r="BT7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3178,1704 +3408,1704 @@
   <dimension ref="A1:DI697"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1"/>
-    <col min="9" max="9" width="10.75" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1"/>
-    <col min="17" max="17" width="21.5" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1"/>
-    <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="20.58203125" customWidth="1"/>
-    <col min="43" max="45" width="11.83203125" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1"/>
-    <col min="47" max="47" width="12.25" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="7" customWidth="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1"/>
-    <col min="54" max="54" width="19.75" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1"/>
-    <col min="56" max="56" width="8.5" customWidth="1"/>
-    <col min="57" max="57" width="13.5" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1"/>
-    <col min="60" max="60" width="8.25" customWidth="1"/>
-    <col min="61" max="61" width="8.33203125" customWidth="1"/>
-    <col min="62" max="62" width="10.1640625" customWidth="1"/>
-    <col min="63" max="67" width="8.33203125" customWidth="1"/>
-    <col min="68" max="70" width="11.25" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1"/>
-    <col min="72" max="73" width="8" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1"/>
-    <col min="75" max="76" width="8.5" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1"/>
-    <col min="80" max="80" width="13.5" customWidth="1"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1"/>
-    <col min="82" max="82" width="15.75" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1"/>
-    <col min="86" max="86" width="9" customWidth="1"/>
-    <col min="87" max="87" width="16" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1"/>
-    <col min="93" max="98" width="9" customWidth="1"/>
-    <col min="99" max="99" width="14" customWidth="1"/>
-    <col min="100" max="100" width="8" customWidth="1"/>
-    <col min="101" max="101" width="9" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1"/>
-    <col min="103" max="103" width="13.75" customWidth="1"/>
-    <col min="104" max="109" width="9" customWidth="1"/>
-    <col min="110" max="110" width="15.5" customWidth="1"/>
-    <col min="111" max="113" width="9" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
+    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="15" customWidth="1" style="2"/>
+    <col min="41" max="41" width="18" customWidth="1" style="2"/>
+    <col min="42" max="42" width="20.58203125" customWidth="1" style="2"/>
+    <col min="43" max="45" width="11.83203125" customWidth="1" style="2"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="7" customWidth="1" style="2"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
+    <col min="61" max="61" width="8.33203125" customWidth="1" style="2"/>
+    <col min="62" max="62" width="10.1640625" customWidth="1" style="2"/>
+    <col min="63" max="67" width="8.33203125" customWidth="1" style="2"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
+    <col min="72" max="73" width="8" customWidth="1" style="2"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
+    <col min="86" max="86" width="9" customWidth="1" style="2"/>
+    <col min="87" max="87" width="16" customWidth="1" style="2"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
+    <col min="93" max="98" width="9" customWidth="1" style="2"/>
+    <col min="99" max="99" width="14" customWidth="1" style="2"/>
+    <col min="100" max="100" width="8" customWidth="1" style="2"/>
+    <col min="101" max="101" width="9" customWidth="1" style="2"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
+    <col min="104" max="109" width="9" customWidth="1" style="2"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
+    <col min="111" max="113" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E1" t="s">
+    <row r="1">
+      <c r="B1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G1" t="s">
+      <c r="E1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H1" t="s">
+      <c r="F1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I1" t="s">
+      <c r="G1" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="L1" t="s">
+      <c r="J1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="M1" t="s">
+      <c r="K1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N1" t="s">
+      <c r="L1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="O1" t="s">
+      <c r="M1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="P1" t="s">
+      <c r="N1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="O1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="R1" t="s">
+      <c r="P1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="T1" t="s">
+      <c r="R1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="U1" t="s">
-        <v>166</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="S1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="W1" t="s">
+      <c r="T1" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="X1" t="s">
+      <c r="U1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="W1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="X1" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>205</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BJ1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="BK1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BV1" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BW1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="BX1" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="BY1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CA1" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CB1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CC1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CD1" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CE1" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CF1" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CG1" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CH1" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CI1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CK1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CM1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CN1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CO1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="CR1" t="s">
-        <v>215</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CP1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CR1" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="CS1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CT1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CU1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CV1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CW1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>244</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="CX1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="CY1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="CZ1" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="DA1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DB1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DC1" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DD1" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DE1" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DF1" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DG1" s="2" t="s">
         <v>254</v>
       </c>
+      <c r="DH1" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="DI1" s="2" t="s">
+        <v>256</v>
+      </c>
     </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F2" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J2" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="M2" t="s">
+      <c r="K2" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="N2" t="s">
+      <c r="L2" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="O2" t="s">
+      <c r="M2" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N2" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="O2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="R2" t="s">
+      <c r="P2" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="S2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="T2" t="s">
+      <c r="R2" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="U2" t="s">
+      <c r="S2" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="V2" t="s">
+      <c r="T2" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="W2" t="s">
+      <c r="U2" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="X2" t="s">
+      <c r="V2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="W2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="X2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BO2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BR2" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="BU2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BS2" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BV2" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BW2" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="BX2" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="BY2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CA2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CC2" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CD2" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CH2" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CI2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CK2" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CM2" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CN2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CP2" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CQ2" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CR2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CS2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CT2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CU2" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CV2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CW2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="CX2" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="CY2" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="CZ2" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DA2" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DB2" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DC2" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DD2" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DE2" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DF2" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="DI2" t="s">
+      <c r="DG2" s="2" t="s">
         <v>360</v>
       </c>
+      <c r="DH2" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="DI2" s="2" t="s">
+        <v>362</v>
+      </c>
     </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" t="s">
-        <v>361</v>
-      </c>
-      <c r="K3" t="s">
-        <v>362</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="I3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="K3" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="P3" t="s">
+      <c r="N3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="O3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R3" t="s">
+      <c r="AD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="S3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" t="s">
-        <v>116</v>
-      </c>
-      <c r="U3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" t="s">
-        <v>116</v>
-      </c>
-      <c r="W3" t="s">
-        <v>115</v>
-      </c>
-      <c r="X3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>364</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AL3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="CB3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="CC3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="CS3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CT3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CU3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CV3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="CW3" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="CY3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="CZ3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DA3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DB3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DC3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="DD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DE3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DF3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DG3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DH3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DI3" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="X6" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="BP6" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="BD7" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN7" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="CR7" s="2">
+        <v>9999</v>
+      </c>
+      <c r="DD7" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG7" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="BD8" s="2">
+        <v>1</v>
+      </c>
+      <c r="CU8" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="DD8" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG8" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="BD9" s="2">
+        <v>1</v>
+      </c>
+      <c r="CU9" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="DD9" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG9" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV11" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD11" s="2">
+        <v>99</v>
+      </c>
+      <c r="CN11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="CR11" s="2">
+        <v>9999</v>
+      </c>
+      <c r="DD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AT12" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="BD12" s="2">
+        <v>99</v>
+      </c>
+      <c r="BP12" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="CN12" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="CR12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="DD12" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG12" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="AT14" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="BD14" s="2">
+        <v>1</v>
+      </c>
+      <c r="BT14" s="2">
+        <v>99999</v>
+      </c>
+      <c r="BV14" s="2">
+        <v>1</v>
+      </c>
+      <c r="BW14" s="2">
+        <v>1</v>
+      </c>
+      <c r="BX14" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="CN14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="CR14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="DD14" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG14" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="AR16" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="AV16" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD16" s="2">
         <v>3</v>
       </c>
-      <c r="AK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>365</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>366</v>
-      </c>
-      <c r="AQ3" t="s">
+      <c r="BO16" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="BP16" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="CU16" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="DD16" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG16" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AV18" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD18" s="2">
+        <v>12</v>
+      </c>
+      <c r="CU18" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="DD18" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG18" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AV19" s="2">
+        <v>20</v>
+      </c>
+      <c r="BD19" s="2">
+        <v>99</v>
+      </c>
+      <c r="CN19" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="CR19" s="2">
+        <v>1</v>
+      </c>
+      <c r="DD19" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG19" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="AC21" s="2">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>367</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>368</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>367</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>369</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>370</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>371</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>371</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>372</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>373</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>374</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>375</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>375</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>372</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>376</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>377</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>377</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>376</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>376</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>376</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>376</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>376</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DG3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>115</v>
+      <c r="AD21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="AX21" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="AZ21" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="CG21" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="CH21" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="CI21" s="2" t="s">
+        <v>421</v>
       </c>
     </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>378</v>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="BO23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BT23" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="BV23" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW23" s="2">
+        <v>6</v>
+      </c>
+      <c r="BX23" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY23" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="CN23" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="CR23" s="2">
+        <v>9999</v>
       </c>
     </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" t="s">
-        <v>379</v>
-      </c>
-      <c r="D6" t="s">
-        <v>380</v>
-      </c>
-      <c r="E6" t="s">
-        <v>381</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>382</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>383</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>384</v>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>426</v>
       </c>
     </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" t="s">
-        <v>385</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>382</v>
-      </c>
-      <c r="L7" t="s">
-        <v>386</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AF7">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>387</v>
-      </c>
-      <c r="BD7">
-        <v>1</v>
-      </c>
-      <c r="CN7" t="s">
-        <v>388</v>
-      </c>
-      <c r="CR7">
-        <v>9999</v>
-      </c>
-      <c r="DD7">
-        <v>1</v>
-      </c>
-      <c r="DG7">
-        <v>1</v>
-      </c>
-      <c r="DH7">
-        <v>1</v>
+    <row r="677">
+      <c r="CL677" s="2">
+        <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>389</v>
-      </c>
-      <c r="C8" t="s">
-        <v>390</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>382</v>
-      </c>
-      <c r="L8" t="s">
-        <v>391</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>387</v>
-      </c>
-      <c r="BD8">
-        <v>1</v>
-      </c>
-      <c r="CU8" t="s">
-        <v>392</v>
-      </c>
-      <c r="DD8">
-        <v>1</v>
-      </c>
-      <c r="DG8">
-        <v>1</v>
-      </c>
-      <c r="DH8">
-        <v>1</v>
+    <row r="679">
+      <c r="CL679" s="2">
+        <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>393</v>
-      </c>
-      <c r="C9" t="s">
-        <v>390</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>382</v>
-      </c>
-      <c r="L9" t="s">
-        <v>386</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>387</v>
-      </c>
-      <c r="BD9">
-        <v>1</v>
-      </c>
-      <c r="CU9" t="s">
-        <v>394</v>
-      </c>
-      <c r="DD9">
-        <v>1</v>
-      </c>
-      <c r="DG9">
-        <v>1</v>
-      </c>
-      <c r="DH9">
-        <v>1</v>
+    <row r="680">
+      <c r="CL680" s="2">
+        <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>395</v>
-      </c>
-      <c r="C11" t="s">
-        <v>385</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>397</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AV11">
-        <v>20</v>
-      </c>
-      <c r="BD11">
-        <v>99</v>
-      </c>
-      <c r="CN11" t="s">
-        <v>396</v>
-      </c>
-      <c r="CR11">
-        <v>9999</v>
-      </c>
-      <c r="DD11">
-        <v>1</v>
-      </c>
-      <c r="DG11">
-        <v>1</v>
-      </c>
-      <c r="DH11">
-        <v>1</v>
+    <row r="682">
+      <c r="CL682" s="2">
+        <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>398</v>
-      </c>
-      <c r="C12" t="s">
-        <v>385</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>382</v>
-      </c>
-      <c r="AC12">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>397</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>141</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>399</v>
-      </c>
-      <c r="BD12">
-        <v>99</v>
-      </c>
-      <c r="BP12" t="s">
-        <v>400</v>
-      </c>
-      <c r="CN12" t="s">
-        <v>396</v>
-      </c>
-      <c r="CR12">
-        <v>9999</v>
-      </c>
-      <c r="DD12">
-        <v>1</v>
-      </c>
-      <c r="DG12">
-        <v>1</v>
-      </c>
-      <c r="DH12">
+    <row r="689">
+      <c r="CL689" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" t="s">
-        <v>385</v>
-      </c>
-      <c r="D14" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" t="s">
-        <v>401</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
-        <v>402</v>
-      </c>
-      <c r="K14" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC14">
-        <v>1</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>387</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>399</v>
-      </c>
-      <c r="BD14">
-        <v>1</v>
-      </c>
-      <c r="BT14">
-        <v>99999</v>
-      </c>
-      <c r="BV14">
-        <v>1</v>
-      </c>
-      <c r="BW14">
-        <v>1</v>
-      </c>
-      <c r="BX14">
-        <v>1</v>
-      </c>
-      <c r="BY14" t="s">
-        <v>404</v>
-      </c>
-      <c r="CN14" t="s">
-        <v>142</v>
-      </c>
-      <c r="CR14">
-        <v>9999</v>
-      </c>
-      <c r="DD14">
-        <v>1</v>
-      </c>
-      <c r="DG14">
-        <v>1</v>
-      </c>
-      <c r="DH14">
-        <v>1</v>
+    <row r="691">
+      <c r="CL691" s="2">
+        <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>400</v>
-      </c>
-      <c r="C16" t="s">
-        <v>405</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="s">
-        <v>382</v>
-      </c>
-      <c r="AC16">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>397</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>406</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>407</v>
-      </c>
-      <c r="AV16">
-        <v>20</v>
-      </c>
-      <c r="BD16">
-        <v>3</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>408</v>
-      </c>
-      <c r="BP16" t="s">
-        <v>408</v>
-      </c>
-      <c r="CU16" t="s">
-        <v>409</v>
-      </c>
-      <c r="DD16">
-        <v>1</v>
-      </c>
-      <c r="DG16">
-        <v>1</v>
-      </c>
-      <c r="DH16">
-        <v>1</v>
+    <row r="692">
+      <c r="CL692" s="2">
+        <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>410</v>
-      </c>
-      <c r="C18" t="s">
-        <v>411</v>
-      </c>
-      <c r="D18" t="s">
-        <v>410</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="K18" t="s">
-        <v>382</v>
-      </c>
-      <c r="L18" t="s">
-        <v>391</v>
-      </c>
-      <c r="AC18">
-        <v>1</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>397</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>144</v>
-      </c>
-      <c r="AV18">
-        <v>20</v>
-      </c>
-      <c r="BD18">
-        <v>12</v>
-      </c>
-      <c r="CU18" t="s">
-        <v>412</v>
-      </c>
-      <c r="DD18">
-        <v>1</v>
-      </c>
-      <c r="DG18">
-        <v>1</v>
-      </c>
-      <c r="DH18">
-        <v>1</v>
+    <row r="695">
+      <c r="CL695" s="2">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>408</v>
-      </c>
-      <c r="C19" t="s">
-        <v>385</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="K19" t="s">
-        <v>382</v>
-      </c>
-      <c r="L19" t="s">
-        <v>386</v>
-      </c>
-      <c r="AC19">
-        <v>1</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>397</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>144</v>
-      </c>
-      <c r="AV19">
-        <v>20</v>
-      </c>
-      <c r="BD19">
-        <v>99</v>
-      </c>
-      <c r="CN19" t="s">
-        <v>413</v>
-      </c>
-      <c r="CR19">
-        <v>1</v>
-      </c>
-      <c r="DD19">
-        <v>1</v>
-      </c>
-      <c r="DG19">
-        <v>1</v>
-      </c>
-      <c r="DH19">
-        <v>1</v>
+    <row r="696">
+      <c r="CL696" s="2">
+        <v>0.667</v>
       </c>
     </row>
-    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>414</v>
-      </c>
-      <c r="C21" t="s">
-        <v>385</v>
-      </c>
-      <c r="AC21">
-        <v>2</v>
-      </c>
-      <c r="AD21">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>415</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>416</v>
-      </c>
-      <c r="AZ21">
-        <v>1</v>
-      </c>
-      <c r="BD21">
-        <v>1</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>56</v>
-      </c>
-      <c r="CG21" t="s">
-        <v>417</v>
-      </c>
-      <c r="CH21" t="s">
-        <v>418</v>
-      </c>
-      <c r="CI21" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>420</v>
-      </c>
-      <c r="C23" t="s">
-        <v>385</v>
-      </c>
-      <c r="D23" t="s">
-        <v>420</v>
-      </c>
-      <c r="E23" t="s">
-        <v>421</v>
-      </c>
-      <c r="G23">
-        <v>3</v>
-      </c>
-      <c r="J23" t="s">
-        <v>402</v>
-      </c>
-      <c r="K23" t="s">
-        <v>422</v>
-      </c>
-      <c r="BO23" t="s">
-        <v>130</v>
-      </c>
-      <c r="BP23" t="s">
-        <v>130</v>
-      </c>
-      <c r="BT23">
-        <v>0.1</v>
-      </c>
-      <c r="BV23">
-        <v>0</v>
-      </c>
-      <c r="BW23">
-        <v>6</v>
-      </c>
-      <c r="BX23">
-        <v>1</v>
-      </c>
-      <c r="BY23" t="s">
-        <v>403</v>
-      </c>
-      <c r="CN23" t="s">
-        <v>423</v>
-      </c>
-      <c r="CR23">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="677" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL677">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="679" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL679">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="680" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL680">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="682" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL682">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL689">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="691" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL691">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="692" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL692">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="695" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL695">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="696" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL696">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="697" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL697">
+    <row r="697">
+      <c r="CL697" s="2">
         <v>0.2</v>
       </c>
     </row>
@@ -4883,6 +5113,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4892,211 +5123,211 @@
   <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
+    <col min="3" max="6" width="9" customWidth="1" style="2"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
+    <col min="8" max="8" width="15" customWidth="1" style="2"/>
+    <col min="9" max="13" width="9" customWidth="1" style="2"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F1" t="s">
-        <v>426</v>
-      </c>
-      <c r="G1" t="s">
-        <v>427</v>
-      </c>
-      <c r="H1" t="s">
-        <v>428</v>
-      </c>
-      <c r="I1" t="s">
-        <v>429</v>
-      </c>
-      <c r="J1" t="s">
-        <v>430</v>
-      </c>
-      <c r="L1" t="s">
-        <v>431</v>
-      </c>
-      <c r="M1" t="s">
-        <v>432</v>
-      </c>
-      <c r="N1" t="s">
-        <v>433</v>
-      </c>
-      <c r="O1" t="s">
-        <v>434</v>
-      </c>
-      <c r="P1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F2" t="s">
-        <v>437</v>
-      </c>
-      <c r="G2" t="s">
-        <v>438</v>
-      </c>
-      <c r="H2" t="s">
-        <v>439</v>
-      </c>
-      <c r="I2" t="s">
-        <v>440</v>
-      </c>
-      <c r="J2" t="s">
-        <v>441</v>
-      </c>
-      <c r="K2" t="s">
-        <v>442</v>
-      </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" t="s">
-        <v>443</v>
-      </c>
-      <c r="N2" t="s">
-        <v>444</v>
-      </c>
-      <c r="O2" t="s">
-        <v>445</v>
-      </c>
-      <c r="P2" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" t="s">
-        <v>376</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>340</v>
-      </c>
-      <c r="M3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N3" t="s">
-        <v>115</v>
-      </c>
-      <c r="O3" t="s">
-        <v>340</v>
-      </c>
-      <c r="P3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>448</v>
-      </c>
-      <c r="C6" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>396</v>
-      </c>
-      <c r="C7" t="s">
-        <v>450</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>453</v>
-      </c>
-      <c r="C8" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C10" t="s">
-        <v>454</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
+      <c r="C10" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5104,6 +5335,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5112,52 +5344,53 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>455</v>
+      <c r="C1" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D2" t="s">
-        <v>346</v>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
+      <c r="C3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5166,86 +5399,87 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="10" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I1" t="s">
-        <v>231</v>
+    <row r="1">
+      <c r="I1" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>458</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="I2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J2" t="s">
-        <v>346</v>
+      <c r="G2" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>375</v>
-      </c>
-      <c r="J3" t="s">
-        <v>124</v>
+      <c r="E3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5254,129 +5488,130 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28" customWidth="1" style="2"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
+    <col min="12" max="12" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C1" t="s">
-        <v>462</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C1" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="L1" t="s">
+      <c r="J1" s="2" t="s">
         <v>470</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>472</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="J2" t="s">
+      <c r="H2" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="K2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L2" t="s">
-        <v>96</v>
+      <c r="I2" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
-        <v>480</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>116</v>
+      <c r="F3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5386,49 +5621,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
+    <col min="7" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="H2" t="s">
-        <v>284</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="E2" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="J2" t="s">
-        <v>53</v>
+      <c r="F2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5442,27 +5677,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5471,107 +5707,108 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1"/>
-    <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1"/>
-    <col min="8" max="8" width="32.25" customWidth="1"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C1" t="s">
-        <v>486</v>
-      </c>
-      <c r="D1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B1" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C1" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D1" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="2" t="s">
         <v>492</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>495</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C2" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D2" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F2" s="2" t="s">
         <v>500</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>503</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/Diy优胜/恶堕凛视.xlsx
+++ b/Excel/Diy优胜/恶堕凛视.xlsx
@@ -326,7 +326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
   <si>
     <t>Id</t>
   </si>
@@ -673,6 +673,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -689,6 +692,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -1903,11 +1909,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2221,30 +2230,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2257,7 +2266,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV7"/>
+  <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2327,13 +2336,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2505,6 +2516,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2725,6 +2738,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2734,7 +2753,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2742,91 +2761,91 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AD3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>2</v>
@@ -2835,10 +2854,10 @@
         <v>2</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AN3" s="2" t="s">
         <v>2</v>
@@ -2847,50 +2866,50 @@
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BF3" s="2" t="s">
         <v>2</v>
@@ -2905,43 +2924,49 @@
         <v>2</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -3019,19 +3044,21 @@
       <c r="BT4" s="2"/>
       <c r="BU4" s="2"/>
       <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -3092,23 +3119,23 @@
         <v>4</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR5" s="2">
         <v>1</v>
@@ -3130,20 +3157,20 @@
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF5" s="2"/>
       <c r="BG5" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BH5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BK5" s="2">
         <v>6</v>
@@ -3152,38 +3179,40 @@
       <c r="BM5" s="2"/>
       <c r="BN5" s="2"/>
       <c r="BO5" s="2"/>
-      <c r="BP5" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="BP5" s="2"/>
       <c r="BQ5" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="BR5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BS5" s="2"/>
       <c r="BT5" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BU5" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BV5" s="2">
+        <v>150</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G6" s="2">
         <v>0.5</v>
@@ -3243,20 +3272,20 @@
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AR6" s="2">
         <v>0</v>
@@ -3278,20 +3307,20 @@
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF6" s="2"/>
       <c r="BG6" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BH6" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BI6" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BJ6" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BK6" s="2">
         <v>6</v>
@@ -3300,38 +3329,40 @@
       <c r="BM6" s="2"/>
       <c r="BN6" s="2"/>
       <c r="BO6" s="2"/>
-      <c r="BP6" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="BP6" s="2"/>
       <c r="BQ6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="BR6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BS6" s="2"/>
       <c r="BT6" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BU6" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BV6" s="2">
+        <v>150</v>
+      </c>
+      <c r="BV6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -3393,20 +3424,20 @@
       <c r="AH7" s="2"/>
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL7" s="2"/>
       <c r="AM7" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN7" s="2"/>
       <c r="AO7" s="2"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR7" s="2">
         <v>0</v>
@@ -3430,20 +3461,20 @@
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF7" s="2"/>
       <c r="BG7" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BH7" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BI7" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BJ7" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BK7" s="2">
         <v>6</v>
@@ -3452,7 +3483,7 @@
       <c r="BM7" s="2"/>
       <c r="BN7" s="2"/>
       <c r="BO7" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BP7" s="2"/>
       <c r="BQ7" s="2"/>
@@ -3461,6 +3492,8 @@
       <c r="BT7" s="2"/>
       <c r="BU7" s="2"/>
       <c r="BV7" s="2"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
@@ -3476,1704 +3509,1704 @@
   <dimension ref="A1:DI697"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="20.58203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="10.75" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="18" customWidth="1" style="2"/>
-    <col min="42" max="42" width="20.58203125" customWidth="1" style="2"/>
-    <col min="43" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="61" width="8.33203125" customWidth="1" style="2"/>
-    <col min="62" max="62" width="10.1640625" customWidth="1" style="2"/>
-    <col min="63" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="113" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="20.58203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="10.75" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="18" customWidth="1" style="3"/>
+    <col min="42" max="42" width="20.58203125" customWidth="1" style="3"/>
+    <col min="43" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="61" width="8.33203125" customWidth="1" style="3"/>
+    <col min="62" max="62" width="10.1640625" customWidth="1" style="3"/>
+    <col min="63" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
+    <col min="93" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="113" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>263</v>
+      </c>
+      <c r="DH1" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>369</v>
+      </c>
+      <c r="DH2" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="U3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AW3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AJ3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="CH3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>122</v>
+      <c r="CS3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>387</v>
+      <c r="A4" s="3" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="X6" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="BP6" s="2" t="s">
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>393</v>
+      </c>
+      <c r="X6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO6" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="BP6" s="3" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="2" t="s">
+      <c r="A7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="BD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN7" s="2" t="s">
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="CR7" s="2">
+      <c r="AC7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN7" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="CR7" s="3">
         <v>9999</v>
       </c>
-      <c r="DD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG7" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH7" s="2">
+      <c r="DD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG7" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="BD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU8" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="DD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG8" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH8" s="2">
+      <c r="BD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU8" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="DD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG8" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH8" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="BD9" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU9" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="DD9" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG9" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH9" s="2">
+      <c r="A9" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="BD9" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU9" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="DD9" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG9" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH9" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="AJ11" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AV11" s="2">
+      <c r="C11" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ11" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV11" s="3">
         <v>20</v>
       </c>
-      <c r="BD11" s="2">
+      <c r="BD11" s="3">
         <v>99</v>
       </c>
-      <c r="CN11" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="CR11" s="2">
+      <c r="CN11" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="CR11" s="3">
         <v>9999</v>
       </c>
-      <c r="DD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG11" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH11" s="2">
+      <c r="DD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH11" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AT12" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>99</v>
+      </c>
+      <c r="BP12" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="CN12" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AJ12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AT12" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="BD12" s="2">
-        <v>99</v>
-      </c>
-      <c r="BP12" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="CN12" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="CR12" s="2">
+      <c r="CR12" s="3">
         <v>9999</v>
       </c>
-      <c r="DD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG12" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH12" s="2">
+      <c r="DD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG12" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH12" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="A14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AT14" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AT14" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="BD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BT14" s="2">
+      <c r="BD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BT14" s="3">
         <v>99999</v>
       </c>
-      <c r="BV14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BW14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BX14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY14" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="CN14" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="CR14" s="2">
+      <c r="BV14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="CN14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="CR14" s="3">
         <v>9999</v>
       </c>
-      <c r="DD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG14" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH14" s="2">
+      <c r="DD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG14" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH14" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AJ16" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AO16" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AR16" s="2" t="s">
+      <c r="A16" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="AV16" s="2">
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AO16" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AR16" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AV16" s="3">
         <v>20</v>
       </c>
-      <c r="BD16" s="2">
+      <c r="BD16" s="3">
         <v>3</v>
       </c>
-      <c r="BO16" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="BP16" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="CU16" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="DD16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH16" s="2">
+      <c r="BO16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="BP16" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="CU16" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="DD16" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG16" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH16" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AV18" s="2">
+      <c r="A18" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AV18" s="3">
         <v>20</v>
       </c>
-      <c r="BD18" s="2">
+      <c r="BD18" s="3">
         <v>12</v>
       </c>
-      <c r="CU18" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="DD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG18" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH18" s="2">
+      <c r="CU18" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="DD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG18" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH18" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AV19" s="2">
+      <c r="A19" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ19" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AV19" s="3">
         <v>20</v>
       </c>
-      <c r="BD19" s="2">
+      <c r="BD19" s="3">
         <v>99</v>
       </c>
-      <c r="CN19" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="CR19" s="2">
-        <v>1</v>
-      </c>
-      <c r="DD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG19" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH19" s="2">
+      <c r="CN19" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="CR19" s="3">
+        <v>1</v>
+      </c>
+      <c r="DD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG19" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH19" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC21" s="2">
+      <c r="A21" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC21" s="3">
         <v>2</v>
       </c>
-      <c r="AD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO21" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="AX21" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="AZ21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB21" s="2" t="s">
+      <c r="AD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="AX21" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="AZ21" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="CG21" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="CH21" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="CI21" s="2" t="s">
+      <c r="CG21" s="3" t="s">
         <v>428</v>
+      </c>
+      <c r="CH21" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="CI21" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="G23" s="2">
+      <c r="A23" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G23" s="3">
         <v>3</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="BO23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="BT23" s="2">
+      <c r="J23" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="BO23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="BP23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="BT23" s="3">
         <v>0.1</v>
       </c>
-      <c r="BV23" s="2">
+      <c r="BV23" s="3">
         <v>0</v>
       </c>
-      <c r="BW23" s="2">
+      <c r="BW23" s="3">
         <v>6</v>
       </c>
-      <c r="BX23" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY23" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="CN23" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="CR23" s="2">
+      <c r="BX23" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY23" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="CN23" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="CR23" s="3">
         <v>9999</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>433</v>
+      <c r="A24" s="3" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="677">
-      <c r="CL677" s="2">
+      <c r="CL677" s="3">
         <v>0.15</v>
       </c>
     </row>
     <row r="679">
-      <c r="CL679" s="2">
+      <c r="CL679" s="3">
         <v>0.2</v>
       </c>
     </row>
     <row r="680">
-      <c r="CL680" s="2">
+      <c r="CL680" s="3">
         <v>0.1</v>
       </c>
     </row>
     <row r="682">
-      <c r="CL682" s="2">
+      <c r="CL682" s="3">
         <v>0.2</v>
       </c>
     </row>
     <row r="689">
-      <c r="CL689" s="2">
+      <c r="CL689" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="691">
-      <c r="CL691" s="2">
+      <c r="CL691" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="692">
-      <c r="CL692" s="2">
+      <c r="CL692" s="3">
         <v>0.6</v>
       </c>
     </row>
     <row r="695">
-      <c r="CL695" s="2">
+      <c r="CL695" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="696">
-      <c r="CL696" s="2">
+      <c r="CL696" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="697">
-      <c r="CL697" s="2">
+      <c r="CL697" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -5191,211 +5224,211 @@
   <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>444</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>355</v>
+      <c r="O2" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>132</v>
+      <c r="L3" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>456</v>
+      <c r="A5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>458</v>
+      <c r="A6" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q7" s="2" t="s">
+      <c r="A7" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>461</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>458</v>
+      <c r="A8" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="A10" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5412,46 +5445,46 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>464</v>
+      <c r="C1" s="3" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>355</v>
+      <c r="C2" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
+      <c r="C3" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5467,80 +5500,80 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>240</v>
+      <c r="I1" s="3" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>355</v>
+      <c r="G2" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>132</v>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5556,123 +5589,123 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>479</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -5689,45 +5722,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5745,22 +5778,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -5775,101 +5808,101 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1" style="2"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="20.58203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1" style="2"/>
-    <col min="5" max="5" width="37.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="39.5" customWidth="1" style="2"/>
-    <col min="7" max="7" width="38.58203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="32.25" customWidth="1" style="2"/>
-    <col min="9" max="9" width="39.9140625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1" style="3"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1" style="3"/>
+    <col min="5" max="5" width="37.58203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="39.5" customWidth="1" style="3"/>
+    <col min="7" max="7" width="38.58203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="32.25" customWidth="1" style="3"/>
+    <col min="9" max="9" width="39.9140625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>501</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>509</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
